--- a/canada-strong/canada_strong_content_review.xlsx
+++ b/canada-strong/canada_strong_content_review.xlsx
@@ -135,7 +135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -154,7 +154,7 @@
     <row r="3" spans="1:1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">This workbook has two working tabs plus this one.</t>
+          <t xml:space="preserve">Last checked against the source files on 2026-09-03.</t>
         </is>
       </c>
     </row>
@@ -162,199 +162,199 @@
       <c r="A4" s="12"/>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This workbook has two working tabs plus this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="12"/>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">TAB: Content Review</t>
         </is>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="8" spans="1:1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  One row per piece of interface text (questions, labels, headings, body copy),</t>
         </is>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="9" spans="1:1">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  English next to French. Use this tab to comment on wording, tone, or translation.</t>
         </is>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="12"/>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="11" t="inlineStr">
+    <row r="10" spans="1:1">
+      <c r="A10" s="12"/>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">TAB: Decision Tree</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Shows which selections lead to which results. The wizard has 4 questions - Need,</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Region, Size, Sector - and the results page is built from several independent</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  blocks of content. Each block is driven by only one or two of the four questions;</t>
+          <t xml:space="preserve">  Shows which selections lead to which results. The wizard has 4 questions - Need,</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the other questions do not change that block, and are marked (any).</t>
+          <t xml:space="preserve">  Region, Size, Sector - and the results page is built from several independent</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="12"/>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  blocks of content. Each block is driven by only one or two of the four questions;</t>
+        </is>
+      </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The blocks, in the order they appear on the results page:</t>
+          <t xml:space="preserve">  the other questions do not change that block, and are marked (any).</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1. Sector-specific programs      - depends on Need + Sector</t>
-        </is>
-      </c>
+      <c r="A16" s="12"/>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2. Sector-agnostic programs      - depends on Need only (always shown)</t>
+          <t xml:space="preserve">  Note: Question 2 (region) now has 7 answers, not 6 - Ontario was split into</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3. Regional programs             - depends on Need + Region</t>
+          <t xml:space="preserve">  Northern Ontario and Southern Ontario, each its own answer with its own RDA link,</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4. Sector hub links              - depends on Sector only</t>
+          <t xml:space="preserve">  because FedNor and FedDev Ontario are two separate agencies. The Prairies answer</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5. Always-on hub links           - shown on every path, no matter what</t>
+          <t xml:space="preserve">  was also relabelled to "Manitoba, Saskatchewan, Alberta" (same region underneath).</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    6. Eligibility - fixed criteria  - always the same, regardless of answers</t>
-        </is>
-      </c>
+      <c r="A21" s="12"/>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    7. Eligibility badges by size    - depends on Size (Q3) only</t>
+          <t xml:space="preserve">  The blocks, in the order they appear on the results page:</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    8. Eligibility badge by sector   - depends on Sector (Q4) only</t>
+          <t xml:space="preserve">    1. Sector-specific programs      - depends on Need + Sector</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="12"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2. Sector-agnostic programs      - depends on Need only (always shown)</t>
+        </is>
+      </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  To trace one full click-through: pick a Need + Sector row in block 1 (the main</t>
+          <t xml:space="preserve">    3. Regional programs             - depends on Need + Region</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  program panel), then read the matching Need row in block 2, the matching</t>
+          <t xml:space="preserve">    4. Sector hub links              - depends on Sector only</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Need + Region row in block 3, the matching Sector row in block 4, block 5 as-is,</t>
+          <t xml:space="preserve">    5. Always-on hub links           - shown on every path, no matter what</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  and the matching Size row in block 7 plus Sector row in block 8. Together those</t>
+          <t xml:space="preserve">    6. Eligibility - fixed criteria  - always the same, regardless of answers</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  give everything shown on that path.</t>
+          <t xml:space="preserve">    7. Eligibility badges by size    - depends on Size (Q3) only</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="12"/>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    8. Eligibility badge by sector   - depends on Sector (Q4) only</t>
+        </is>
+      </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Use the Comments column here to flag routing that looks wrong (a program missing</t>
+          <t xml:space="preserve">    9. Eligibility panel - RDA note  - depends on Region (Q2) only (new)</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  or misplaced for a given selection), separate from wording issues in Content Review.</t>
-        </is>
-      </c>
+      <c r="A32" s="12"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="12"/>
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Note: as of 2026-09-03, a sector + need combination with no matching program</t>
+        </is>
+      </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Both tabs: set Status to Needs change if flagging something for a fix, or Approved</t>
+          <t xml:space="preserve">  (block 1) shows nothing at all - the old "No stream specific to your sector"</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">once happy with a row. Leave as Open otherwise. Add your name under Reviewer.</t>
+          <t xml:space="preserve">  notice was removed. Those rows are marked "(nothing shown here)" below.</t>
         </is>
       </c>
     </row>
@@ -362,35 +362,138 @@
       <c r="A36" s="12"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Source files:</t>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Note: block 9 is new - once any region is picked, a one-line note naming that</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+          <t xml:space="preserve">  region's development agency (with a link) is appended at the bottom of the</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+          <t xml:space="preserve">  Eligibility criteria panel, after the checklist and the Large Enterprise note.</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  It does not depend on Need, Size, or Sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="12"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  To trace one full click-through: pick a Need + Sector row in block 1 (the main</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  program panel), then read the matching Need row in block 2, the matching</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Need + Region row in block 3, the matching Sector row in block 4, block 5 as-is,</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the matching Size row in block 7, Sector row in block 8, and Region row in block 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Together those give everything shown on that path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="12"/>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Use the Comments column here to flag routing that looks wrong (a program missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  or misplaced for a given selection), separate from wording issues in Content Review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="12"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both tabs: set Status to Needs change if flagging something for a fix, or Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">once happy with a row. Leave as Open otherwise. Add your name under Reviewer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="12"/>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source files:</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">  canada-strong/_data/tariff_tool_links.csv  (the program list behind the Decision Tree tab)</t>
         </is>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="58" spans="1:1">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  canada-strong/business-en.html  (the template that assembles the results page)</t>
         </is>
@@ -402,7 +505,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -744,22 +847,22 @@
     <row r="12" spans="1:7">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.title</t>
+          <t xml:space="preserve">regions.reg-atl.rda</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find support for tariff impacts</t>
+          <t xml:space="preserve">Atlantic Canada Opportunities Agency</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouver du soutien face aux droits de douane</t>
+          <t xml:space="preserve">Agence de promotion économique du Canada atlantique</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -773,22 +876,22 @@
     <row r="13" spans="1:7">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.description</t>
+          <t xml:space="preserve">regions.reg-qc.rda</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the federal supports available to businesses, employers and workers affected by United States tariffs.</t>
+          <t xml:space="preserve">Canada Economic Development for Quebec Regions</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouvez les mesures de soutien fédérales offertes aux entreprises, aux employeurs et aux travailleurs touchés par les droits de douane américains.</t>
+          <t xml:space="preserve">Développement économique Canada pour les régions du Québec</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -802,22 +905,22 @@
     <row r="14" spans="1:7">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.h1</t>
+          <t xml:space="preserve">regions.reg-on-n.rda</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find support for tariff impacts</t>
+          <t xml:space="preserve">Federal Economic Development Agency for Northern Ontario</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouver du soutien face aux droits de douane</t>
+          <t xml:space="preserve">Agence fédérale de développement économique pour le Nord de l'Ontario</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -831,22 +934,22 @@
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.intro</t>
+          <t xml:space="preserve">regions.reg-on-s.rda</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the support you need</t>
+          <t xml:space="preserve">Federal Economic Development Agency for Southern Ontario</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouvez le soutien qu'il vous faut</t>
+          <t xml:space="preserve">Agence fédérale de développement économique pour le Sud de l'Ontario</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -860,22 +963,22 @@
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.options[0].label</t>
+          <t xml:space="preserve">regions.reg-pr.rda</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">I am a business or employer</t>
+          <t xml:space="preserve">Prairies Economic Development Canada</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Je suis une entreprise ou un employeur</t>
+          <t xml:space="preserve">Développement économique Canada pour les Prairies</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -889,22 +992,22 @@
     <row r="17" spans="1:7">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.options[0].description</t>
+          <t xml:space="preserve">regions.reg-bc.rda</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer four questions about need, region, size and sector</t>
+          <t xml:space="preserve">PacifiCan</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Répondez à quatre questions sur votre besoin, votre région, votre taille et votre secteur</t>
+          <t xml:space="preserve">PacifiCan</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -918,22 +1021,22 @@
     <row r="18" spans="1:7">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.options[0].cta</t>
+          <t xml:space="preserve">regions.reg-nor.rda</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Build me a short list</t>
+          <t xml:space="preserve">Canadian Northern Economic Development Agency</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dressez ma liste</t>
+          <t xml:space="preserve">Agence canadienne de développement économique du Nord</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -945,198 +1048,198 @@
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Start page</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start.options[1].label</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I am a worker</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis un travailleur ou une travailleuse</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="2"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start.title</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find support for tariff impacts</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trouver du soutien face aux droits de douane</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Start page</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start.options[1].description</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reach income support, skills training and student aid directly</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accédez directement au soutien du revenu, à la formation et à l'aide aux étudiants</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="2"/>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start.description</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find the federal supports available to businesses, employers and workers affected by United States tariffs.</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trouvez les mesures de soutien fédérales offertes aux entreprises, aux employeurs et aux travailleurs touchés par les droits de douane américains.</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="6"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Start page</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start.options[1].cta</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Show me worker supports</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Montrez-moi le soutien aux travailleurs</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="2"/>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start.h1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find support for tariff impacts</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trouver du soutien face aux droits de douane</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="6"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Start page</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start.options[2].label</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I want more information</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je veux plus d'information</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="2"/>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start.intro</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find the support you need</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trouvez le soutien qu'il vous faut</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F22" s="9"/>
+      <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Start page</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start.options[2].description</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">General overview of Canada's response to U.S. tariffs</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aperçu général de la réponse du Canada aux droits de douane américains</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="2"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start.options[0].label</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I am a business or employer</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis une entreprise ou un employeur</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F23" s="9"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Start page</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start.options[2].cta</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Give me the overview</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Donnez-moi l'aperçu</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="2"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start.options[0].description</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answer four questions about need, region, size and sector</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Répondez à quatre questions sur votre besoin, votre région, votre taille et votre secteur</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F24" s="9"/>
+      <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Business wizard - general</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.title</t>
+          <t xml:space="preserve">start.options[0].cta</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find support for your business</t>
+          <t xml:space="preserve">Build me a short list</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouver du soutien pour votre entreprise</t>
+          <t xml:space="preserve">Dressez ma liste</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -1150,22 +1253,22 @@
     <row r="26" spans="1:7">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - general</t>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.description</t>
+          <t xml:space="preserve">start.options[1].label</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer four questions to get a shortlist of federal programs for businesses affected by United States tariffs.</t>
+          <t xml:space="preserve">I am a worker</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Répondez à quatre questions pour obtenir une liste de programmes fédéraux destinés aux entreprises touchées par les droits de douane américains.</t>
+          <t xml:space="preserve">Je suis un travailleur ou une travailleuse</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1179,22 +1282,22 @@
     <row r="27" spans="1:7">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - general</t>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.h1</t>
+          <t xml:space="preserve">start.options[1].description</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find support for your business</t>
+          <t xml:space="preserve">Reach income support, skills training and student aid directly</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouver du soutien pour votre entreprise</t>
+          <t xml:space="preserve">Accédez directement au soutien du revenu, à la formation et à l'aide aux étudiants</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1208,22 +1311,22 @@
     <row r="28" spans="1:7">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - general</t>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.intro</t>
+          <t xml:space="preserve">start.options[1].cta</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer four questions and we will show you the programs that fit your need, your region, your size and your sector.</t>
+          <t xml:space="preserve">Show me worker supports</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Répondez à quatre questions et nous vous montrerons les programmes qui correspondent à votre besoin, à votre région, à votre taille et à votre secteur.</t>
+          <t xml:space="preserve">Montrez-moi le soutien aux travailleurs</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1237,22 +1340,22 @@
     <row r="29" spans="1:7">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - general</t>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.questions_heading</t>
+          <t xml:space="preserve">start.options[2].label</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tell us about your business</t>
+          <t xml:space="preserve">I want more information</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parlez-nous de votre entreprise</t>
+          <t xml:space="preserve">Je veux plus d'information</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -1266,22 +1369,22 @@
     <row r="30" spans="1:7">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - general</t>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.results_heading</t>
+          <t xml:space="preserve">start.options[2].description</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programs that match your answers</t>
+          <t xml:space="preserve">General overview of Canada's response to U.S. tariffs</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programmes correspondant à vos réponses</t>
+          <t xml:space="preserve">Aperçu général de la réponse du Canada aux droits de douane américains</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -1295,22 +1398,22 @@
     <row r="31" spans="1:7">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - general</t>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.back_link</t>
+          <t xml:space="preserve">start.options[2].cta</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start over</t>
+          <t xml:space="preserve">Give me the overview</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recommencer</t>
+          <t xml:space="preserve">Donnez-moi l'aperçu</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -1324,22 +1427,22 @@
     <row r="32" spans="1:7">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.agnostic_suffix</t>
+          <t xml:space="preserve">business.title</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">open to all sectors</t>
+          <t xml:space="preserve">Find support for your business</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tous secteurs confondus</t>
+          <t xml:space="preserve">Trouver du soutien pour votre entreprise</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -1353,22 +1456,22 @@
     <row r="33" spans="1:7">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.route_heading</t>
+          <t xml:space="preserve">business.description</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No stream specific to your sector</t>
+          <t xml:space="preserve">Answer four questions to get a shortlist of federal programs for businesses affected by United States tariffs.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aucun volet propre à votre secteur</t>
+          <t xml:space="preserve">Répondez à quatre questions pour obtenir une liste de programmes fédéraux destinés aux entreprises touchées par les droits de douane américains.</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -1382,22 +1485,22 @@
     <row r="34" spans="1:7">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.route_body</t>
+          <t xml:space="preserve">business.h1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">Find support for your business</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">Trouver du soutien pour votre entreprise</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1411,22 +1514,22 @@
     <row r="35" spans="1:7">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.region_heading</t>
+          <t xml:space="preserve">business.intro</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programs for your region</t>
+          <t xml:space="preserve">Answer four questions and we will show you the programs that fit your need, your region, your size and your sector.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programmes pour votre région</t>
+          <t xml:space="preserve">Répondez à quatre questions et nous vous montrerons les programmes qui correspondent à votre besoin, à votre région, à votre taille et à votre secteur.</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -1440,22 +1543,22 @@
     <row r="36" spans="1:7">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.region_footnote</t>
+          <t xml:space="preserve">business.questions_heading</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional criteria and intake dates vary.</t>
+          <t xml:space="preserve">Tell us about your business</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les critères régionaux et les dates de réception des demandes varient.</t>
+          <t xml:space="preserve">Parlez-nous de votre entreprise</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -1469,22 +1572,22 @@
     <row r="37" spans="1:7">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.hub_heading</t>
+          <t xml:space="preserve">business.results_heading</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Where these programs are listed</t>
+          <t xml:space="preserve">Programs that match your answers</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Où ces programmes sont répertoriés</t>
+          <t xml:space="preserve">Programmes correspondant à vos réponses</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -1498,22 +1601,22 @@
     <row r="38" spans="1:7">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.hub_body</t>
+          <t xml:space="preserve">business.back_link</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">These hubs are the departments' own lists. They are kept current, so check them if something here looks out of date.</t>
+          <t xml:space="preserve">Start over</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ces carrefours sont les listes tenues par les ministères eux-mêmes. Ils sont à jour : consultez-les si une information ici semble désuète.</t>
+          <t xml:space="preserve">Recommencer</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -1527,22 +1630,22 @@
     <row r="39" spans="1:7">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 - need</t>
+          <t xml:space="preserve">Business wizard - result labels</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.questions.question-1.legend</t>
+          <t xml:space="preserve">business.labels.agnostic_suffix</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 of 4: What do you need right now?</t>
+          <t xml:space="preserve">open to all sectors</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 sur 4 : De quoi avez-vous besoin en ce moment?</t>
+          <t xml:space="preserve">tous secteurs confondus</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -1556,22 +1659,22 @@
     <row r="40" spans="1:7">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 - need</t>
+          <t xml:space="preserve">Business wizard - result labels</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-1.option[need-fin]</t>
+          <t xml:space="preserve">business.labels.region_heading</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financing to keep operating or grow</t>
+          <t xml:space="preserve">Programs for your region</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du financement pour poursuivre vos activités ou prendre de l'expansion</t>
+          <t xml:space="preserve">Programmes pour votre région</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -1585,22 +1688,22 @@
     <row r="41" spans="1:7">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 - need</t>
+          <t xml:space="preserve">Business wizard - result labels</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-1.option[need-liq]</t>
+          <t xml:space="preserve">business.labels.region_footnote</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+          <t xml:space="preserve">Regional criteria and intake dates vary.</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Des liquidités pour combler un manque de trésorerie causé par les droits de douane</t>
+          <t xml:space="preserve">Les critères régionaux et les dates de réception des demandes varient.</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -1614,22 +1717,22 @@
     <row r="42" spans="1:7">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 - need</t>
+          <t xml:space="preserve">Business wizard - result labels</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-1.option[need-tra]</t>
+          <t xml:space="preserve">business.labels.hub_heading</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Where these programs are listed</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un projet de transformation ou d'immobilisations</t>
+          <t xml:space="preserve">Où ces programmes sont répertoriés</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -1643,22 +1746,22 @@
     <row r="43" spans="1:7">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 - need</t>
+          <t xml:space="preserve">Business wizard - result labels</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-1.option[need-wrk]</t>
+          <t xml:space="preserve">business.labels.hub_body</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
+          <t xml:space="preserve">These hubs are the departments' own lists. They are kept current, so check them if something here looks out of date.</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le maintien en poste et le recyclage de votre main-d'œuvre</t>
+          <t xml:space="preserve">Ces carrefours sont les listes tenues par les ministères eux-mêmes. Ils sont à jour : consultez-les si une information ici semble désuète.</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -1670,53 +1773,53 @@
       <c r="G43" s="6"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 2 - region</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.questions.question-2.legend</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 2 of 4: Where is your business located?</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 2 sur 4 : Où votre entreprise est-elle située?</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F44" s="5"/>
-      <c r="G44" s="2"/>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business wizard - result labels</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">business.labels.rda_prefix</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: </t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : </t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F44" s="9"/>
+      <c r="G44" s="6"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 2 - region</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 1 - need</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-atl]</t>
+          <t xml:space="preserve">business.questions.question-1.legend</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantic</t>
+          <t xml:space="preserve">Question 1 of 4: What do you need right now?</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantique</t>
+          <t xml:space="preserve">Question 1 sur 4 : De quoi avez-vous besoin en ce moment?</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -1730,22 +1833,22 @@
     <row r="46" spans="1:7">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 2 - region</t>
+          <t xml:space="preserve">Question 1 - need</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-qc]</t>
+          <t xml:space="preserve">question-1.option[need-fin]</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">Financing to keep operating or grow</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Québec</t>
+          <t xml:space="preserve">Du financement pour poursuivre vos activités ou prendre de l'expansion</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -1759,22 +1862,22 @@
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 2 - region</t>
+          <t xml:space="preserve">Question 1 - need</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-on]</t>
+          <t xml:space="preserve">question-1.option[need-liq]</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontario</t>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontario</t>
+          <t xml:space="preserve">Des liquidités pour combler un manque de trésorerie causé par les droits de douane</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -1788,22 +1891,22 @@
     <row r="48" spans="1:7">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 2 - region</t>
+          <t xml:space="preserve">Question 1 - need</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-pr]</t>
+          <t xml:space="preserve">question-1.option[need-tra]</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prairies</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prairies</t>
+          <t xml:space="preserve">Un projet de transformation ou d'immobilisations</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -1817,22 +1920,22 @@
     <row r="49" spans="1:7">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 2 - region</t>
+          <t xml:space="preserve">Question 1 - need</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-bc]</t>
+          <t xml:space="preserve">question-1.option[need-wrk]</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Workforce retention and retraining</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colombie-Britannique</t>
+          <t xml:space="preserve">Le maintien en poste et le recyclage de votre main-d'œuvre</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -1844,53 +1947,53 @@
       <c r="G49" s="2"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-2.option[reg-nor]</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The North</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le Nord</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F50" s="5"/>
-      <c r="G50" s="2"/>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">business.questions.question-2.legend</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 2 of 4: Where is your business located?</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 2 sur 4 : Où votre entreprise est-elle située?</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F50" s="9"/>
+      <c r="G50" s="6"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 3 - size</t>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.questions.question-3.legend</t>
+          <t xml:space="preserve">question-2.option[reg-atl]</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 3 of 4: What is your size and revenue?</t>
+          <t xml:space="preserve">Atlantic</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 3 sur 4 : Quels sont votre taille et vos revenus?</t>
+          <t xml:space="preserve">Atlantique</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -1904,22 +2007,22 @@
     <row r="52" spans="1:7">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 3 - size</t>
+          <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-under1m]</t>
+          <t xml:space="preserve">question-2.option[reg-qc]</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under $1 million in annual revenue</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moins de 1 million de dollars de revenus annuels</t>
+          <t xml:space="preserve">Québec</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -1933,22 +2036,22 @@
     <row r="53" spans="1:7">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 3 - size</t>
+          <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-1to5m]</t>
+          <t xml:space="preserve">question-2.option[reg-on-n]</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">De 1 à 5 millions de dollars et 3 ans ou plus d'activité</t>
+          <t xml:space="preserve">Nord de l'Ontario (y compris Parry Sound)</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -1962,22 +2065,22 @@
     <row r="54" spans="1:7">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 3 - size</t>
+          <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-5mplus]</t>
+          <t xml:space="preserve">question-2.option[reg-on-s]</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 millions de dollars ou plus et 10 employés à temps plein ou plus</t>
+          <t xml:space="preserve">Sud de l'Ontario (au sud de Muskoka)</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -1991,22 +2094,22 @@
     <row r="55" spans="1:7">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 3 - size</t>
+          <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-large]</t>
+          <t xml:space="preserve">question-2.option[reg-pr]</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Large enterprise</t>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grande entreprise</t>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -2018,82 +2121,82 @@
       <c r="G55" s="6"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 - sector</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.questions.question-4.legend</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 of 4: What is your sector and tariff impact?</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 sur 4 : Quel est votre secteur et quelle est l'incidence des droits de douane?</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F56" s="5"/>
-      <c r="G56" s="2"/>
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 2 - region</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-2.option[reg-bc]</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">British Columbia</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colombie-Britannique</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F56" s="9"/>
+      <c r="G56" s="6"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 - sector</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-4.option[sec-forestry]</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forestry and softwood lumber</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Foresterie et bois d'œuvre</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F57" s="5"/>
-      <c r="G57" s="2"/>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 2 - region</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-2.option[reg-nor]</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The North</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Nord</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F57" s="9"/>
+      <c r="G57" s="6"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 - sector</t>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 3 - size</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-steel]</t>
+          <t xml:space="preserve">business.questions.question-3.legend</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
+          <t xml:space="preserve">Question 3 of 4: What is your size and revenue?</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acier, aluminium et cuivre</t>
+          <t xml:space="preserve">Question 3 sur 4 : Quels sont votre taille et vos revenus?</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -2107,22 +2210,22 @@
     <row r="59" spans="1:7">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 4 - sector</t>
+          <t xml:space="preserve">Question 3 - size</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-mfg]</t>
+          <t xml:space="preserve">question-3.option[size-under1m]</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
+          <t xml:space="preserve">Under $1 million in annual revenue</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabrication et autres exportateurs</t>
+          <t xml:space="preserve">Moins de 1 million de dollars de revenus annuels</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -2136,22 +2239,22 @@
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 4 - sector</t>
+          <t xml:space="preserve">Question 3 - size</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-agri]</t>
+          <t xml:space="preserve">question-3.option[size-1to5m]</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agroalimentaire, poisson et fruits de mer</t>
+          <t xml:space="preserve">De 1 à 5 millions de dollars et 3 ans ou plus d'activité</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -2165,22 +2268,22 @@
     <row r="61" spans="1:7">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 4 - sector</t>
+          <t xml:space="preserve">Question 3 - size</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-usexport]</t>
+          <t xml:space="preserve">question-3.option[size-5mplus]</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exportations vers les États-Unis représentant 15 % ou plus de vos revenus</t>
+          <t xml:space="preserve">5 millions de dollars ou plus et 10 employés à temps plein ou plus</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -2192,53 +2295,53 @@
       <c r="G61" s="2"/>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.eligibility.heading</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Critères d'admissibilité</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F62" s="9"/>
-      <c r="G62" s="6"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 3 - size</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-3.option[size-large]</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large enterprise</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grande entreprise</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F62" s="5"/>
+      <c r="G62" s="2"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.eligibility.body</t>
+          <t xml:space="preserve">business.questions.question-4.legend</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programs on this page commonly apply these criteria. This is a guide, not a decision - the program you apply to makes the final determination.</t>
+          <t xml:space="preserve">Question 4 of 4: What is your sector and tariff impact?</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les programmes de cette page appliquent couramment ces critères. Il s'agit d'un guide et non d'une décision : le programme auquel vous présentez une demande rend la décision finale.</t>
+          <t xml:space="preserve">Question 4 sur 4 : Quel est votre secteur et quelle est l'incidence des droits de douane?</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -2252,22 +2355,22 @@
     <row r="64" spans="1:7">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility checklist</t>
+          <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[0].text (incorporation)</t>
+          <t xml:space="preserve">question-4.option[sec-forestry]</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Canadian-incorporated</t>
+          <t xml:space="preserve">Forestry and softwood lumber</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Constituée en société au Canada</t>
+          <t xml:space="preserve">Foresterie et bois d'œuvre</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -2281,22 +2384,22 @@
     <row r="65" spans="1:7">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility checklist</t>
+          <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[1].text (years operating)</t>
+          <t xml:space="preserve">question-4.option[sec-steel]</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 or more years operating</t>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 ans ou plus d'activité</t>
+          <t xml:space="preserve">Acier, aluminium et cuivre</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -2310,22 +2413,22 @@
     <row r="66" spans="1:7">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility checklist</t>
+          <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[2].text (revenue)</t>
+          <t xml:space="preserve">question-4.option[sec-mfg]</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$1 million or more in annual revenue</t>
+          <t xml:space="preserve">Manufacturing and other exporters</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 million de dollars ou plus de revenus annuels</t>
+          <t xml:space="preserve">Fabrication et autres exportateurs</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -2339,22 +2442,22 @@
     <row r="67" spans="1:7">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility checklist</t>
+          <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[3].text (cash flow)</t>
+          <t xml:space="preserve">question-4.option[sec-agri]</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive cash flow</t>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flux de trésorerie positif</t>
+          <t xml:space="preserve">Agriculture, agroalimentaire, poisson et fruits de mer</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -2368,22 +2471,22 @@
     <row r="68" spans="1:7">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility checklist</t>
+          <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[4].text (US export/tariff impact)</t>
+          <t xml:space="preserve">question-4.option[sec-usexport]</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15% or more of revenue from U.S. exports, or a 10% tariff-driven revenue decline or cost increase</t>
+          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 % ou plus des revenus provenant d'exportations vers les États-Unis, ou une baisse de revenus ou une hausse de coûts de 10 % attribuable aux droits de douane</t>
+          <t xml:space="preserve">Exportations vers les États-Unis représentant 15 % ou plus de vos revenus</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -2395,53 +2498,53 @@
       <c r="G68" s="6"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility checklist</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.eligibility.large_note</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size.</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille.</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F69" s="9"/>
-      <c r="G69" s="6"/>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">business.eligibility.heading</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critères d'admissibilité</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F69" s="5"/>
+      <c r="G69" s="2"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility badges</t>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility checklist</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">badge[met] (years/revenue/US export)</t>
+          <t xml:space="preserve">business.eligibility.body</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Met</t>
+          <t xml:space="preserve">Programs on this page commonly apply these criteria. This is a guide, not a decision - the program you apply to makes the final determination.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Satisfait</t>
+          <t xml:space="preserve">Les programmes de cette page appliquent couramment ces critères. Il s'agit d'un guide et non d'une décision : le programme auquel vous présentez une demande rend la décision finale.</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -2455,22 +2558,22 @@
     <row r="71" spans="1:7">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility badges</t>
+          <t xml:space="preserve">Eligibility checklist</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">badge[review] (incorporation/years/cash flow/US export)</t>
+          <t xml:space="preserve">criteria[0].text (incorporation)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Needs review</t>
+          <t xml:space="preserve">Canadian-incorporated</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">À vérifier</t>
+          <t xml:space="preserve">Constituée en société au Canada</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -2484,22 +2587,22 @@
     <row r="72" spans="1:7">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility badges</t>
+          <t xml:space="preserve">Eligibility checklist</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">badge[notmet] (revenue)</t>
+          <t xml:space="preserve">criteria[1].text (years operating)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not met</t>
+          <t xml:space="preserve">3 or more years operating</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non satisfait</t>
+          <t xml:space="preserve">3 ans ou plus d'activité</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -2510,10 +2613,213 @@
       <c r="F72" s="5"/>
       <c r="G72" s="2"/>
     </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility checklist</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">criteria[2].text (revenue)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$1 million or more in annual revenue</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 million de dollars ou plus de revenus annuels</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F73" s="5"/>
+      <c r="G73" s="2"/>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility checklist</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">criteria[3].text (cash flow)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive cash flow</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flux de trésorerie positif</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F74" s="5"/>
+      <c r="G74" s="2"/>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility checklist</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">criteria[4].text (US export/tariff impact)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15% or more of revenue from U.S. exports, or a 10% tariff-driven revenue decline or cost increase</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 % ou plus des revenus provenant d'exportations vers les États-Unis, ou une baisse de revenus ou une hausse de coûts de 10 % attribuable aux droits de douane</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F75" s="5"/>
+      <c r="G75" s="2"/>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility checklist</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">business.eligibility.large_note</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille.</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F76" s="5"/>
+      <c r="G76" s="2"/>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility badges</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badge[met] (years/revenue/US export)</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Met</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Satisfait</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F77" s="9"/>
+      <c r="G77" s="6"/>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility badges</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badge[review] (incorporation/years/cash flow/US export)</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs review</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À vérifier</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F78" s="9"/>
+      <c r="G78" s="6"/>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility badges</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badge[notmet] (revenue)</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not met</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non satisfait</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F79" s="9"/>
+      <c r="G79" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G72"/>
+  <autoFilter ref="A1:G79"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E72">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E79">
       <formula1>"Open,Needs change,Approved"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2522,16 +2828,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="8" width="46" customWidth="1"/>
     <col min="9" max="9" width="46" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
@@ -2634,17 +2940,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Route notice: "No stream specific to your sector"</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -2688,17 +2994,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Route notice: "No stream specific to your sector"</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
@@ -3246,17 +3552,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Route notice: "No stream specific to your sector"</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -3470,17 +3776,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Route notice: "No stream specific to your sector"</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -3524,17 +3830,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Route notice: "No stream specific to your sector"</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -3632,17 +3938,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Route notice: "No stream specific to your sector"</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -4077,7 +4383,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontario</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -4131,7 +4437,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prairies</t>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4185,7 +4491,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4239,7 +4545,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4288,12 +4594,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+          <t xml:space="preserve">Financing to keep operating or grow</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantic</t>
+          <t xml:space="preserve">The North</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4308,17 +4614,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programs for your region</t>
+          <t xml:space="preserve">(no regional panel)</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Atlantic (ACOA / APECA)</t>
+          <t xml:space="preserve">(none - financing has no region-specific program)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire au Canada atlantique (ACOA / APECA)</t>
+          <t xml:space="preserve">(aucun - le financement n'a pas de programme régional)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -4347,7 +4653,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">Atlantic</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4367,12 +4673,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Quebec (CED / DEC)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Atlantic (ACOA / APECA)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Québec (CED / DEC)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire au Canada atlantique (ACOA / APECA)</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -4401,7 +4707,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontario</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4421,14 +4727,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Southern Ontario (FedDev Ontario)
-Regional Tariff Response Initiative - Northern Ontario (FedNor)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Quebec (CED / DEC)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire dans le Sud de l'Ontario (FedDev Ontario)
-Initiative régionale de réponse tarifaire – Nord de l'Ontario (FedNor)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Québec (CED / DEC)</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -4457,7 +4761,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prairies</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4477,12 +4781,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Prairies (PrairiesCan)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Northern Ontario (FedNor)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire (IRRT) pour la région des Prairies (PrairiesCan)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord de l'Ontario (FedNor)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -4511,7 +4815,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4531,12 +4835,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - British Columbia (PacifiCan)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Southern Ontario (FedDev Ontario)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire en Colombie-Britannique (PacifiCan)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire dans le Sud de l'Ontario (FedDev Ontario)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -4565,7 +4869,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4585,12 +4889,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - North (CanNor)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Prairies (PrairiesCan)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord (CanNor)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire (IRRT) pour la région des Prairies (PrairiesCan)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -4614,12 +4918,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantic</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4639,12 +4943,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Atlantic (ACOA / APECA)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - British Columbia (PacifiCan)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire au Canada atlantique (ACOA / APECA)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire en Colombie-Britannique (PacifiCan)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -4668,12 +4972,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">The North</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4693,12 +4997,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Quebec (CED / DEC)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - North (CanNor)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Québec (CED / DEC)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord (CanNor)</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -4727,7 +5031,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontario</t>
+          <t xml:space="preserve">Atlantic</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4747,14 +5051,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Southern Ontario (FedDev Ontario)
-Regional Tariff Response Initiative - Northern Ontario (FedNor)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Atlantic (ACOA / APECA)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire dans le Sud de l'Ontario (FedDev Ontario)
-Initiative régionale de réponse tarifaire – Nord de l'Ontario (FedNor)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire au Canada atlantique (ACOA / APECA)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -4783,7 +5085,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prairies</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4803,12 +5105,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Prairies (PrairiesCan)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Quebec (CED / DEC)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire (IRRT) pour la région des Prairies (PrairiesCan)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Québec (CED / DEC)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -4837,7 +5139,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4857,12 +5159,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - British Columbia (PacifiCan)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Northern Ontario (FedNor)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire en Colombie-Britannique (PacifiCan)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord de l'Ontario (FedNor)</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -4891,7 +5193,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4911,12 +5213,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - North (CanNor)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Southern Ontario (FedDev Ontario)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord (CanNor)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire dans le Sud de l'Ontario (FedDev Ontario)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -4940,12 +5242,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantic</t>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4960,17 +5262,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no regional panel)</t>
+          <t xml:space="preserve">Programs for your region</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Prairies (PrairiesCan)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire (IRRT) pour la région des Prairies (PrairiesCan)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -4994,12 +5296,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5014,17 +5316,17 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no regional panel)</t>
+          <t xml:space="preserve">Programs for your region</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - British Columbia (PacifiCan)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire en Colombie-Britannique (PacifiCan)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -5048,12 +5350,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontario</t>
+          <t xml:space="preserve">The North</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5068,17 +5370,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no regional panel)</t>
+          <t xml:space="preserve">Programs for your region</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - North (CanNor)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord (CanNor)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -5107,7 +5409,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prairies</t>
+          <t xml:space="preserve">Atlantic</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5161,7 +5463,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5215,7 +5517,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5252,935 +5554,935 @@
       <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Regional programs</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q2 Region</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workforce retention and retraining</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no regional panel)</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K50" s="5"/>
+      <c r="L50" s="2"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Regional programs</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q2 Region</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workforce retention and retraining</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no regional panel)</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K51" s="5"/>
+      <c r="L51" s="2"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Regional programs</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q2 Region</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workforce retention and retraining</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">British Columbia</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no regional panel)</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K52" s="5"/>
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Regional programs</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q2 Region</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workforce retention and retraining</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The North</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no regional panel)</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K53" s="5"/>
+      <c r="L53" s="2"/>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Sector hub links</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Forestry and softwood lumber</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Forestry and lumber: where these programs are listed</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Support for forest sector employers and workers (hub) (NRCan)</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Soutien fédéral aux entreprises et aux travailleurs du secteur forestier (NRCan)</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K50" s="9"/>
-      <c r="L50" s="6"/>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K54" s="9"/>
+      <c r="L54" s="6"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Sector hub links</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Steel and aluminum: where these programs are listed</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Support for the Canadian steel sector (Finance Canada)</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Soutien au secteur canadien de l'acier (Finance Canada)</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K51" s="9"/>
-      <c r="L51" s="6"/>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K55" s="9"/>
+      <c r="L55" s="6"/>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Sector hub links</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Manufacturing and other exporters</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(no sector hub)</t>
         </is>
       </c>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(none)</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(aucun)</t>
         </is>
       </c>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K52" s="9"/>
-      <c r="L52" s="6"/>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K56" s="9"/>
+      <c r="L56" s="6"/>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Sector hub links</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Agriculture: where these programs are listed</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">AgPal / AgriGuichet (AAFC, third-party hosted)
 Support measures for industries affected by trade disruptions (hub) (AAFC)</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">AgriGuichet (AAFC, hébergé par un tiers)
 Mesures de soutien pour les industries touchées par les perturbations commerciales (AAFC)</t>
         </is>
       </c>
-      <c r="J53" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K53" s="9"/>
-      <c r="L53" s="6"/>
-    </row>
-    <row r="54" spans="1:12">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K57" s="9"/>
+      <c r="L57" s="6"/>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Sector hub links</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(no sector hub)</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(none)</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(aucun)</t>
         </is>
       </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K54" s="9"/>
-      <c r="L54" s="6"/>
-    </row>
-    <row r="55" spans="1:12">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K58" s="9"/>
+      <c r="L58" s="6"/>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">5. Always-on hub links</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">None - shown on every path</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Where these programs are listed</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Benefits Finder (ISED)
 Supports for business (hub) (ISED)
-Support for Canadian workers and employers (UPSTREAM HUB) (Finance Canada)</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
+Support for Canadian workers and employers (Finance Canada)</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Outil de recherche d'aide aux entreprises (ISED)
 Soutien aux entreprises (ISED)
 Soutien aux employeurs et aux travailleurs canadiens en réponse aux droits de douane (Finance Canada)</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K55" s="5"/>
-      <c r="L55" s="2"/>
-    </row>
-    <row r="56" spans="1:12">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K59" s="5"/>
+      <c r="L59" s="2"/>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">6. Eligibility - fixed criteria</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">None - always the same badge</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">"Canadian-incorporated" badge: Needs review</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « Constituée en société au Canada » : À vérifier</t>
         </is>
       </c>
-      <c r="J56" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K56" s="9"/>
-      <c r="L56" s="6"/>
-    </row>
-    <row r="57" spans="1:12">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K60" s="9"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6. Eligibility - fixed criteria</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">None - always the same badge</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">"Positive cash flow" badge: Needs review</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="I61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « Flux de trésorerie positif » : À vérifier</t>
         </is>
       </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K57" s="9"/>
-      <c r="L57" s="6"/>
-    </row>
-    <row r="58" spans="1:12">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K61" s="9"/>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Eligibility badges by size</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 Size only</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Under $1 million in annual revenue</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Needs review
 "$1 million or more in annual revenue" badge: Not met
 Large Enterprise (LETL) note: not shown</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Non satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
         </is>
       </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K58" s="5"/>
-      <c r="L58" s="2"/>
-    </row>
-    <row r="59" spans="1:12">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K62" s="5"/>
+      <c r="L62" s="2"/>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Eligibility badges by size</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 Size only</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Met
 "$1 million or more in annual revenue" badge: Met
 Large Enterprise (LETL) note: not shown</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : Satisfait
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
         </is>
       </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K59" s="5"/>
-      <c r="L59" s="2"/>
-    </row>
-    <row r="60" spans="1:12">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K63" s="5"/>
+      <c r="L63" s="2"/>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Eligibility badges by size</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 Size only</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Needs review
 "$1 million or more in annual revenue" badge: Met
 Large Enterprise (LETL) note: not shown</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
         </is>
       </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K60" s="5"/>
-      <c r="L60" s="2"/>
-    </row>
-    <row r="61" spans="1:12">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K64" s="5"/>
+      <c r="L64" s="2"/>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Eligibility badges by size</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 Size only</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Large enterprise</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Needs review
 "$1 million or more in annual revenue" badge: Met
 Large Enterprise (LETL) note: SHOWN - "As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size."</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : AFFICHÉE - « En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille. »</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K61" s="5"/>
-      <c r="L61" s="2"/>
-    </row>
-    <row r="62" spans="1:12">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K65" s="5"/>
+      <c r="L65" s="2"/>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">8. Eligibility badge by sector</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Forestry and softwood lumber</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
+      <c r="I66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J62" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K62" s="9"/>
-      <c r="L62" s="6"/>
-    </row>
-    <row r="63" spans="1:12">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K63" s="9"/>
-      <c r="L63" s="6"/>
-    </row>
-    <row r="64" spans="1:12">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
-        </is>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J64" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K64" s="9"/>
-      <c r="L64" s="6"/>
-    </row>
-    <row r="65" spans="1:12">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K65" s="9"/>
-      <c r="L65" s="6"/>
-    </row>
-    <row r="66" spans="1:12">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Met</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : Satisfait</t>
         </is>
       </c>
       <c r="J66" s="9" t="inlineStr">
@@ -6191,10 +6493,604 @@
       <c r="K66" s="9"/>
       <c r="L66" s="6"/>
     </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Eligibility badge by sector</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K67" s="9"/>
+      <c r="L67" s="6"/>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Eligibility badge by sector</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manufacturing and other exporters</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K68" s="9"/>
+      <c r="L68" s="6"/>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Eligibility badge by sector</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K69" s="9"/>
+      <c r="L69" s="6"/>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Eligibility badge by sector</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Met</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : Satisfait</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K70" s="9"/>
+      <c r="L70" s="6"/>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atlantic</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Atlantic Canada Opportunities Agency</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence de promotion économique du Canada atlantique</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K71" s="5"/>
+      <c r="L71" s="2"/>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quebec</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Canada Economic Development for Quebec Regions</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les régions du Québec</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K72" s="5"/>
+      <c r="L72" s="2"/>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Northern Ontario</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Nord de l'Ontario</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K73" s="5"/>
+      <c r="L73" s="2"/>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Southern Ontario</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Sud de l'Ontario</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K74" s="5"/>
+      <c r="L74" s="2"/>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Prairies Economic Development Canada</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les Prairies</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K75" s="5"/>
+      <c r="L75" s="2"/>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">British Columbia</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: PacifiCan</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : PacifiCan</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K76" s="5"/>
+      <c r="L76" s="2"/>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The North</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Canadian Northern Economic Development Agency</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence canadienne de développement économique du Nord</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K77" s="5"/>
+      <c r="L77" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L66"/>
+  <autoFilter ref="A1:L77"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J66">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J77">
       <formula1>"Open,Needs change,Approved"</formula1>
     </dataValidation>
   </dataValidations>

--- a/canada-strong/canada_strong_content_review.xlsx
+++ b/canada-strong/canada_strong_content_review.xlsx
@@ -5,6 +5,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Content Review" sheetId="2" r:id="rId2"/>
     <sheet name="Decision Tree" sheetId="3" r:id="rId4"/>
+    <sheet name="Gap Analysis" sheetId="4" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -135,7 +136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -164,7 +165,7 @@
     <row r="5" spans="1:1">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">This workbook has two working tabs plus this one.</t>
+          <t xml:space="preserve">This workbook has three working tabs plus this one.</t>
         </is>
       </c>
     </row>
@@ -448,54 +449,207 @@
       <c r="A50" s="12"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Both tabs: set Status to Needs change if flagging something for a fix, or Approved</t>
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAB: Gap Analysis</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">once happy with a row. Leave as Open otherwise. Add your name under Reviewer.</t>
+          <t xml:space="preserve">  Compares every program named on two live Canada.ca pages - the workers/employers</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="12"/>
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  tariff-support page and the Canada Strong campaign page - against the CSV that</t>
+        </is>
+      </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Source files:</t>
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  drives the wizard, to catch anything the wizard is missing.</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+          <t xml:space="preserve">    1. Missing - employer/business side       - on the source page, not in the CSV</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+          <t xml:space="preserve">    2. Missing - new program (not in the CSV) - Build Communities Strong Fund</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/tariff_tool_links.csv  (the program list behind the Decision Tree tab)</t>
+          <t xml:space="preserve">    3. Missing - worker-facing supports        - out of scope by design: the wizard</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">                                                 only covers the business path, and</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 "I am a worker" on the start page</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 routes straight to that source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 instead of building a list</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    4. Confirmed present                       - already in the wizard; Maps to</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 wizard program names the matching</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 CSV / Decision Tree entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Set Status per row to Add to wizard, Won't add, or leave Open for a call still</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  to be made; rows already in the wizard default to Already covered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="12"/>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Content Review and Decision Tree tabs: set Status to Needs change if flagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">something for a fix, or Approved once happy with a row. Leave as Open otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add your name under Reviewer on any tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="12"/>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source files:</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/tariff_tool_links.csv  (the program list behind the Decision Tree tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">  canada-strong/business-en.html  (the template that assembles the results page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="12"/>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Compared against, for the Gap Analysis tab (checked 2026-09-03):</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  https://www.canada.ca/en/department-finance/programs/international-trade-finance-policy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    canadas-response-us-tariffs/support-canadian-workers-employers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  https://www.canada.ca/en/campaign/canadastrong.html</t>
         </is>
       </c>
     </row>
@@ -7095,4 +7249,1339 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Program / Service</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organization</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Description (from source page)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source page</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maps to wizard program</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reviewer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Missing - employer/business side</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank (ESDC)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resources to help find, hire and retain the right workers, explore the job market and stay informed about employment standards.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Missing - employer/business side</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank - Training Finder</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank (ESDC)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For employers with a Work-Sharing agreement: training and other resources via Job Bank's Training Finder.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Missing - employer/business side</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank - Worker Search Tool</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank (ESDC)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Search an occupation to discover the number of workers looking for a job locally or nationwide.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Missing - employer/business side</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Expanding your business into new markets</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International Canada</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New market entry, reducing risk, trade data and inclusive trade.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(distinct from EDC's Market diversification guide, which IS in the wizard)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Missing - employer/business side</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What importers need to know</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CBSA</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resources for businesses importing goods into Canada.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Missing - employer/business side</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting Canadian exporters</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trade Commissioner Service (GAC)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Explore available resources to navigate U.S. tariffs.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(distinct page from "Support for Canadian exporters faced with U.S. tariffs", which IS in the wizard as the TCS row)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Missing - new program (not in the CSV at all)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build Communities Strong Fund</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(not stated on page)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investing in a wide range of infrastructure projects that support economic prosperity through housing, health, transit, and climate adaptation.</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canada Strong campaign page</t>
+        </is>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporary Employment Insurance (EI) Measures</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measures that improve access to EI benefits, including waiving the one-week EI waiting period.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank (worker-facing)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank (ESDC)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job postings and career opportunities - the leading source for jobs and labour market information.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skills for Success</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Government of Canada</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assess your skills and learn about the skills necessary to succeed in today's evolving labour market.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Training Finder (worker-facing)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank (ESDC)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gain in-demand skills from training courses by recognized Canadian institutions.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skills and employment training for Indigenous people</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Develop your skills and access job training through Indigenous service organizations.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canada Student Grants and Loans</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Government of Canada</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants and loans available to full-time and part-time post-secondary students.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repayment Assistance Plan (RAP)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Government of Canada</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repayment assistance if you are having trouble paying your student loan.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Employment Insurance (EI) and courses or training programs</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Take a course or training program while receiving EI benefits.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canada Apprentice Loan</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Government of Canada</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interest-free loans to help complete an apprenticeship in a designated Red Seal trade.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tax deductions and credits for apprentices</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Government of Canada</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tax deductions and credits for tradespeople, including moving expenses, tuition fees and tool expenses.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EI for apprentices</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Income support during full-time technical training.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work-Sharing Program</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measures for employers experiencing a temporary reduction in business.</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work-Sharing Program (ESDC) - workforce, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H20" s="9"/>
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Student Work Placement Program</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wage subsidies to hire post-secondary students.</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Student Work Placement Program (ESDC) - workforce, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H21" s="9"/>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Worker Retention Grant</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Income support for EI-eligible employees on reduced hours under an approved Work-Sharing agreement.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Worker Retention Grant (ESDC) - workforce, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H22" s="9"/>
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regional Tariff Response Initiative</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regional development agencies</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financial support for small and medium-sized enterprises impacted by tariffs.</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both pages</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regional Tariff Response Initiative (national hub, liquidity/transformation agnostic) + per-region variants in the regional programs block</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H23" s="9"/>
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strategic Response Fund</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISED</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For innovative projects in sectors affected by the U.S. tariffs.</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strategic Response Fund (SRF) (ISED) - transformation, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H24" s="9"/>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEEFC</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loans for large Canadian enterprises affected by current and future tariffs and countermeasures.</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) (CEEFC / CDEV) - liquidity, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H25" s="9"/>
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supports for business</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISED</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loans, grants and tailored programs to help a business expand into new markets.</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supports for business (hub) (ISED) - always-on hub</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H26" s="9"/>
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business Benefits Finder</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISED</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A tailored list of benefits that may be helpful to your business.</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business Benefits Finder (ISED) - always-on hub</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H27" s="9"/>
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Process for requesting remission of tariffs</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finance Canada</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Request exceptional relief from tariffs imposed as part of Canada's countermeasures.</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Process for requesting remission of tariffs (Finance Canada) - liquidity, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H28" s="9"/>
+      <c r="I28" s="6"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support for the Canadian Steel Sector</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finance Canada</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trade measures, financial support and more to help the steel sector.</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support for the Canadian steel sector (Finance Canada) - steel sector hub</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H29" s="9"/>
+      <c r="I29" s="6"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support for forest sector</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Natural Resources Canada</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity support, assistance to affected workers and industry transformation.</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support for forest sector employers and workers (hub) (NRCan) - forestry sector hub</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H30" s="9"/>
+      <c r="I30" s="6"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duties Relief Program</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CBSA</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qualified businesses can apply to import commercial goods without paying duties.</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duties Relief Program (CBSA) - liquidity, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H31" s="9"/>
+      <c r="I31" s="6"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drawback Program</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CBSA</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removing the domestic duty impact from commercial goods to compete in export markets.</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duty Drawback Program (CBSA) - liquidity, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H32" s="9"/>
+      <c r="I32" s="6"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support for Canadian exporters faced with U.S. tariffs</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trade Commissioner Service (GAC)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Help on how to export duty-free to the U.S.</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TCS - US tariffs support for exporters (GAC) - transformation, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H33" s="9"/>
+      <c r="I33" s="6"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Employment Insurance-funded Labour Market Development Agreements (LMDAs)</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Government investments through LMDAs to help workers and employers affected by tariffs access training and employment support.</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workforce Tariff Response - EI-funded LMDAs (ESDC) - workforce, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H34" s="9"/>
+      <c r="I34" s="6"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Services for agri-food exporters (partial match)</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AAFC</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Help for agri-food businesses to export goods - trade shows, in-market expertise and the Canada Brand.</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canada Brand (AAFC) + Trade Commissioner Service (agri-food) (AAFC) - agriculture, transformation block</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H35" s="9"/>
+      <c r="I35" s="6"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I35"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G35">
+      <formula1>"Open,Add to wizard,Won't add,Already covered"</formula1>
+    </dataValidation>
+  </dataValidations>
+</worksheet>
 </file>
--- a/canada-strong/canada_strong_content_review.xlsx
+++ b/canada-strong/canada_strong_content_review.xlsx
@@ -136,7 +136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A81"/>
+  <dimension ref="A1:A93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -155,7 +155,7 @@
     <row r="3" spans="1:1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Last checked against the source files on 2026-09-03.</t>
+          <t xml:space="preserve">Last checked against the source files on 2026-09-03 (commit 04ebf3ee, business size).</t>
         </is>
       </c>
     </row>
@@ -331,323 +331,403 @@
     <row r="31" spans="1:1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    9. Eligibility panel - RDA note  - depends on Region (Q2) only (new)</t>
+          <t xml:space="preserve">    9. Eligibility panel - RDA note  - depends on Region (Q2) only</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="12"/>
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   10. Size-gated line items         - depends on Size (Q3), layered on blocks 1 and 2 (new)</t>
+        </is>
+      </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Note: as of 2026-09-03, a sector + need combination with no matching program</t>
-        </is>
-      </c>
+      <c r="A33" s="12"/>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (block 1) shows nothing at all - the old "No stream specific to your sector"</t>
+          <t xml:space="preserve">  Note: as of 2026-09-03, a sector + need combination with no matching program</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  (block 1) shows nothing at all - the old "No stream specific to your sector"</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">  notice was removed. Those rows are marked "(nothing shown here)" below.</t>
         </is>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="12"/>
-    </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Note: block 9 is new - once any region is picked, a one-line note naming that</t>
-        </is>
-      </c>
+      <c r="A37" s="12"/>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  region's development agency (with a link) is appended at the bottom of the</t>
+          <t xml:space="preserve">  Note: block 9 - once any region is picked, a one-line note naming that region's</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Eligibility criteria panel, after the checklist and the Large Enterprise note.</t>
+          <t xml:space="preserve">  development agency (with a link) is appended at the bottom of the Eligibility</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  It does not depend on Need, Size, or Sector.</t>
+          <t xml:space="preserve">  criteria panel, after the checklist and the Large Enterprise note. It does not</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="12"/>
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  depend on Need, Size, or Sector.</t>
+        </is>
+      </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  To trace one full click-through: pick a Need + Sector row in block 1 (the main</t>
-        </is>
-      </c>
+      <c r="A42" s="12"/>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  program panel), then read the matching Need row in block 2, the matching</t>
+          <t xml:space="preserve">  Note: Question 3 (size) now has a 5th answer, "Non-profit, association, board of</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Need + Region row in block 3, the matching Sector row in block 4, block 5 as-is,</t>
+          <t xml:space="preserve">  trade" - the Regional Tariff Response Initiative is open to these too. And size</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the matching Size row in block 7, Sector row in block 8, and Region row in block 9.</t>
+          <t xml:space="preserve">  can now hide or show individual programs within an already-visible panel, not</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Together those give everything shown on that path.</t>
+          <t xml:space="preserve">  just change eligibility badges: the Large Enterprise Tariff Loan only appears in</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="12"/>
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the Liquidity panel (block 2) for "Large enterprise", and AgriMarketing's SME vs.</t>
+        </is>
+      </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Use the Comments column here to flag routing that looks wrong (a program missing</t>
+          <t xml:space="preserve">  National Industry Association streams in the Agriculture/Transformation panel</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  or misplaced for a given selection), separate from wording issues in Content Review.</t>
+          <t xml:space="preserve">  (block 1) switch on whether "Non-profit..." was picked. Block 1 and block 2's own</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="12"/>
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  rows for those two panels now say so inline; block 10 spells out all 10 size x</t>
+        </is>
+      </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TAB: Gap Analysis</t>
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  panel combinations one at a time.</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Compares every program named on two live Canada.ca pages - the workers/employers</t>
-        </is>
-      </c>
+      <c r="A52" s="12"/>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  tariff-support page and the Canada Strong campaign page - against the CSV that</t>
+          <t xml:space="preserve">  To trace one full click-through: pick a Need + Sector row in block 1 (the main</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  drives the wizard, to catch anything the wizard is missing.</t>
+          <t xml:space="preserve">  program panel), then read the matching Need row in block 2, the matching</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1. Missing - employer/business side       - on the source page, not in the CSV</t>
+          <t xml:space="preserve">  Need + Region row in block 3, the matching Sector row in block 4, block 5 as-is,</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2. Missing - new program (not in the CSV) - Build Communities Strong Fund</t>
+          <t xml:space="preserve">  the matching Size row in block 7, Sector row in block 8, Region row in block 9,</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3. Missing - worker-facing supports        - out of scope by design: the wizard</t>
+          <t xml:space="preserve">  and - if your path touches the Liquidity or Agriculture/Transformation panels -</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 only covers the business path, and</t>
+          <t xml:space="preserve">  your Size row in block 10. Together those give everything shown on that path.</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                 "I am a worker" on the start page</t>
-        </is>
-      </c>
+      <c r="A59" s="12"/>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 routes straight to that source page</t>
+          <t xml:space="preserve">  Use the Comments column here to flag routing that looks wrong (a program missing</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 instead of building a list</t>
+          <t xml:space="preserve">  or misplaced for a given selection), separate from wording issues in Content Review.</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    4. Confirmed present                       - already in the wizard; Maps to</t>
-        </is>
-      </c>
+      <c r="A62" s="12"/>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                 wizard program names the matching</t>
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAB: Gap Analysis</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 CSV / Decision Tree entry</t>
+          <t xml:space="preserve">  Compares every program named on two live Canada.ca pages - the workers/employers</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Set Status per row to Add to wizard, Won't add, or leave Open for a call still</t>
+          <t xml:space="preserve">  tariff-support page and the Canada Strong campaign page - against the CSV that</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  to be made; rows already in the wizard default to Already covered.</t>
+          <t xml:space="preserve">  drives the wizard, to catch anything the wizard is missing.</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="12"/>
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1. Missing - employer/business side       - on the source page, not in the CSV</t>
+        </is>
+      </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content Review and Decision Tree tabs: set Status to Needs change if flagging</t>
+          <t xml:space="preserve">    2. Missing - new program (not in the CSV) - Build Communities Strong Fund</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">something for a fix, or Approved once happy with a row. Leave as Open otherwise.</t>
+          <t xml:space="preserve">    3. Missing - worker-facing supports        - out of scope by design: the wizard</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add your name under Reviewer on any tab.</t>
+          <t xml:space="preserve">                                                 only covers the business path, and</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="12"/>
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 "I am a worker" on the start page</t>
+        </is>
+      </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Source files:</t>
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 routes straight to that source page</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+          <t xml:space="preserve">                                                 instead of building a list</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+          <t xml:space="preserve">    4. Confirmed present                       - already in the wizard; Maps to</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/tariff_tool_links.csv  (the program list behind the Decision Tree tab)</t>
+          <t xml:space="preserve">                                                 wizard program names the matching</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/business-en.html  (the template that assembles the results page)</t>
+          <t xml:space="preserve">                                                 CSV / Decision Tree entry</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="12"/>
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Set Status per row to Add to wizard, Won't add, or leave Open for a call still</t>
+        </is>
+      </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Compared against, for the Gap Analysis tab (checked 2026-09-03):</t>
+          <t xml:space="preserve">  to be made; rows already in the wizard default to Already covered.</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  https://www.canada.ca/en/department-finance/programs/international-trade-finance-policy/</t>
-        </is>
-      </c>
+      <c r="A79" s="12"/>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    canadas-response-us-tariffs/support-canadian-workers-employers.html</t>
+          <t xml:space="preserve">Content Review and Decision Tree tabs: set Status to Needs change if flagging</t>
         </is>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">something for a fix, or Approved once happy with a row. Leave as Open otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add your name under Reviewer on any tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="12"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source files:</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/tariff_tool_links.csv  (the program list behind the Decision Tree tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/business-en.html  (the template that assembles the results page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="12"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Compared against, for the Gap Analysis tab (checked 2026-09-03):</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  https://www.canada.ca/en/department-finance/programs/international-trade-finance-policy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    canadas-response-us-tariffs/support-canadian-workers-employers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  https://www.canada.ca/en/campaign/canadastrong.html</t>
         </is>
@@ -659,7 +739,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2398,17 +2478,17 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-1to5m]</t>
+          <t xml:space="preserve">question-3.option[size-nonprofit]</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
+          <t xml:space="preserve">Non-profit, association, board of trade</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">De 1 à 5 millions de dollars et 3 ans ou plus d'activité</t>
+          <t xml:space="preserve">Organisme sans but lucratif, association, chambre de commerce</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -2427,17 +2507,17 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-5mplus]</t>
+          <t xml:space="preserve">question-3.option[size-1to5m]</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
+          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 millions de dollars ou plus et 10 employés à temps plein ou plus</t>
+          <t xml:space="preserve">De 1 à 5 millions de dollars et 3 ans ou plus d'activité</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -2456,17 +2536,17 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-large]</t>
+          <t xml:space="preserve">question-3.option[size-5mplus]</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Large enterprise</t>
+          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grande entreprise</t>
+          <t xml:space="preserve">5 millions de dollars ou plus et 10 employés à temps plein ou plus</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -2478,53 +2558,53 @@
       <c r="G62" s="2"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 3 - size</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-3.option[size-large]</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large enterprise</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grande entreprise</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F63" s="5"/>
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">business.questions.question-4.legend</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 4 of 4: What is your sector and tariff impact?</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 4 sur 4 : Quel est votre secteur et quelle est l'incidence des droits de douane?</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F63" s="9"/>
-      <c r="G63" s="6"/>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 - sector</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-4.option[sec-forestry]</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forestry and softwood lumber</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Foresterie et bois d'œuvre</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -2543,17 +2623,17 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-steel]</t>
+          <t xml:space="preserve">question-4.option[sec-forestry]</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
+          <t xml:space="preserve">Forestry and softwood lumber</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acier, aluminium et cuivre</t>
+          <t xml:space="preserve">Foresterie et bois d'œuvre</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -2572,17 +2652,17 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-mfg]</t>
+          <t xml:space="preserve">question-4.option[sec-steel]</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabrication et autres exportateurs</t>
+          <t xml:space="preserve">Acier, aluminium et cuivre</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -2601,17 +2681,17 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-agri]</t>
+          <t xml:space="preserve">question-4.option[sec-mfg]</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+          <t xml:space="preserve">Manufacturing and other exporters</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agroalimentaire, poisson et fruits de mer</t>
+          <t xml:space="preserve">Fabrication et autres exportateurs</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -2630,17 +2710,17 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-usexport]</t>
+          <t xml:space="preserve">question-4.option[sec-agri]</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exportations vers les États-Unis représentant 15 % ou plus de vos revenus</t>
+          <t xml:space="preserve">Agriculture, agroalimentaire, poisson et fruits de mer</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -2652,53 +2732,53 @@
       <c r="G68" s="6"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 4 - sector</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-4.option[sec-usexport]</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exportations vers les États-Unis représentant 15 % ou plus de vos revenus</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F69" s="9"/>
+      <c r="G69" s="6"/>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility checklist</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">business.eligibility.heading</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Critères d'admissibilité</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F69" s="5"/>
-      <c r="G69" s="2"/>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.eligibility.body</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Programs on this page commonly apply these criteria. This is a guide, not a decision - the program you apply to makes the final determination.</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les programmes de cette page appliquent couramment ces critères. Il s'agit d'un guide et non d'une décision : le programme auquel vous présentez une demande rend la décision finale.</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -2717,17 +2797,17 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[0].text (incorporation)</t>
+          <t xml:space="preserve">business.eligibility.body</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Canadian-incorporated</t>
+          <t xml:space="preserve">Programs on this page commonly apply these criteria. This is a guide, not a decision - the program you apply to makes the final determination.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Constituée en société au Canada</t>
+          <t xml:space="preserve">Les programmes de cette page appliquent couramment ces critères. Il s'agit d'un guide et non d'une décision : le programme auquel vous présentez une demande rend la décision finale.</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -2746,17 +2826,17 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[1].text (years operating)</t>
+          <t xml:space="preserve">criteria[0].text (incorporation)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 or more years operating</t>
+          <t xml:space="preserve">Canadian-incorporated</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 ans ou plus d'activité</t>
+          <t xml:space="preserve">Constituée en société au Canada</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -2775,17 +2855,17 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[2].text (revenue)</t>
+          <t xml:space="preserve">criteria[1].text (years operating)</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">$1 million or more in annual revenue</t>
+          <t xml:space="preserve">3 or more years operating</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 million de dollars ou plus de revenus annuels</t>
+          <t xml:space="preserve">3 ans ou plus d'activité</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -2804,17 +2884,17 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[3].text (cash flow)</t>
+          <t xml:space="preserve">criteria[2].text (revenue)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive cash flow</t>
+          <t xml:space="preserve">$1 million or more in annual revenue</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flux de trésorerie positif</t>
+          <t xml:space="preserve">1 million de dollars ou plus de revenus annuels</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -2833,17 +2913,17 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[4].text (US export/tariff impact)</t>
+          <t xml:space="preserve">criteria[3].text (cash flow)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15% or more of revenue from U.S. exports, or a 10% tariff-driven revenue decline or cost increase</t>
+          <t xml:space="preserve">Positive cash flow</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 % ou plus des revenus provenant d'exportations vers les États-Unis, ou une baisse de revenus ou une hausse de coûts de 10 % attribuable aux droits de douane</t>
+          <t xml:space="preserve">Flux de trésorerie positif</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -2862,17 +2942,17 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.eligibility.large_note</t>
+          <t xml:space="preserve">criteria[4].text (US export/tariff impact)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size.</t>
+          <t xml:space="preserve">15% or more of revenue from U.S. exports, or a 10% tariff-driven revenue decline or cost increase</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille.</t>
+          <t xml:space="preserve">15 % ou plus des revenus provenant d'exportations vers les États-Unis, ou une baisse de revenus ou une hausse de coûts de 10 % attribuable aux droits de douane</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -2884,53 +2964,53 @@
       <c r="G76" s="2"/>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="7" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility checklist</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">business.eligibility.large_note</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille.</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F77" s="5"/>
+      <c r="G77" s="2"/>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility badges</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">badge[met] (years/revenue/US export)</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Met</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Satisfait</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F77" s="9"/>
-      <c r="G77" s="6"/>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility badges</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badge[review] (incorporation/years/cash flow/US export)</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Needs review</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">À vérifier</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -2949,17 +3029,17 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">badge[notmet] (revenue)</t>
+          <t xml:space="preserve">badge[review] (incorporation/years/cash flow/US export)</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not met</t>
+          <t xml:space="preserve">Needs review</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non satisfait</t>
+          <t xml:space="preserve">À vérifier</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -2970,10 +3050,39 @@
       <c r="F79" s="9"/>
       <c r="G79" s="6"/>
     </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility badges</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badge[notmet] (revenue)</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not met</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non satisfait</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F80" s="9"/>
+      <c r="G80" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G79"/>
+  <autoFilter ref="A1:G80"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E79">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E80">
       <formula1>"Open,Needs change,Approved"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2982,7 +3091,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -3789,7 +3898,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1 Need + Q4 Sector</t>
+          <t xml:space="preserve">Q1 Need + Q4 Sector (2 lines also gated by Q3 Size - see block 10)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3804,7 +3913,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">(any - 2 of these 5 lines are size-gated, see block 10)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3819,8 +3928,8 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AgriMarketing Program: Market Diversification for SMEs (AAFC)
-AgriMarketing Program: Market Diversification for National Industry Associations (AAFC)
+          <t xml:space="preserve">AgriMarketing Program: Market Diversification for SMEs (AAFC) - shown for every Q3 answer EXCEPT "Non-profit, association, board of trade"
+AgriMarketing Program: Market Diversification for National Industry Associations (AAFC) - shown ONLY for "Non-profit, association, board of trade"
 Trade Commissioner Service (agri-food) (AAFC)
 Canada Brand (AAFC)
 Single window contact for agri-food trade services (AAFC)</t>
@@ -3828,8 +3937,8 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programme Agri-marketing : Diversification des marchés pour les petites et moyennes entreprises (AAFC)
-Programme Agri-marketing : Diversification des marchés pour les associations nationales de l'industrie (AAFC)
+          <t xml:space="preserve">Programme Agri-marketing : Diversification des marchés pour les petites et moyennes entreprises (AAFC) - affiché pour toute réponse Q3 SAUF « Organisme sans but lucratif, association, chambre de commerce »
+Programme Agri-marketing : Diversification des marchés pour les associations nationales de l'industrie (AAFC) - affiché UNIQUEMENT pour « Organisme sans but lucratif, association, chambre de commerce »
 Service des délégués commerciaux (AAFC)
 Marque Canada (AAFC)
 Guichet unique pour communiquer avec le Service d'exportation agroalimentaire (AAFC)</t>
@@ -4235,7 +4344,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1 Need only (always shown)</t>
+          <t xml:space="preserve">Q1 Need only (1 line also gated by Q3 Size - see block 10)</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -4250,7 +4359,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">(any - 1 of these 6 lines is size-gated, see block 10)</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -4266,7 +4375,7 @@
       <c r="H23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Pivot to Grow Loan - Liquidity Support stream (BDC)
-Large Enterprise Tariff Loan (LETL) (CEEFC / CDEV)
+Large Enterprise Tariff Loan (LETL) (CEEFC / CDEV) - shown ONLY for "Large enterprise"
 Regional Tariff Response Initiative (national hub) (ISED / RDAs)
 Duties Relief Program (CBSA)
 Duty Drawback Program (CBSA)
@@ -4276,7 +4385,7 @@
       <c r="I23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Prêt Pivoter pour se propulser – volet soutien aux liquidités (BDC)
-Crédit pour les grandes entreprises touchées par les droits de douane (CGETDD) (CEEFC / CDEV)
+Crédit pour les grandes entreprises touchées par les droits de douane (CGETDD) (CEEFC / CDEV) - affiché UNIQUEMENT pour « Grande entreprise »
 Initiative régionale de réponse tarifaire (ISED / RDAs)
 Programme d'exonération des droits (CBSA)
 Programme de drawback (CBSA)
@@ -6442,240 +6551,246 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Non-profit, association, board of trade</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"3 or more years operating" badge: Needs review
+"$1 million or more in annual revenue" badge: Not met
+Large Enterprise (LETL) note: not shown
+(badges borrow size-under1m's as a placeholder - no non-profit-specific guidance yet)</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
+Insigne pour « 1 million de dollars ou plus de revenus annuels » : Non satisfait
+Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée
+(les insignes empruntent ceux de size-under1m comme choix provisoire - aucune orientation propre aux OSBL pour le moment)</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K63" s="5"/>
+      <c r="L63" s="2"/>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7. Eligibility badges by size</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size only</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Met
 "$1 million or more in annual revenue" badge: Met
 Large Enterprise (LETL) note: not shown</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : Satisfait
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K63" s="5"/>
-      <c r="L63" s="2"/>
-    </row>
-    <row r="64" spans="1:12">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K64" s="5"/>
+      <c r="L64" s="2"/>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Eligibility badges by size</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 Size only</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Needs review
 "$1 million or more in annual revenue" badge: Met
 Large Enterprise (LETL) note: not shown</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
         </is>
       </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K64" s="5"/>
-      <c r="L64" s="2"/>
-    </row>
-    <row r="65" spans="1:12">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K65" s="5"/>
+      <c r="L65" s="2"/>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Eligibility badges by size</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 Size only</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Large enterprise</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Needs review
 "$1 million or more in annual revenue" badge: Met
 Large Enterprise (LETL) note: SHOWN - "As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size."</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : AFFICHÉE - « En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille. »</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K65" s="5"/>
-      <c r="L65" s="2"/>
-    </row>
-    <row r="66" spans="1:12">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K66" s="5"/>
+      <c r="L66" s="2"/>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">8. Eligibility badge by sector</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Forestry and softwood lumber</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J66" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K66" s="9"/>
-      <c r="L66" s="6"/>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
@@ -6729,7 +6844,7 @@
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -6783,7 +6898,7 @@
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+          <t xml:space="preserve">Manufacturing and other exporters</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
@@ -6837,7 +6952,7 @@
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -6847,12 +6962,12 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Met</t>
+          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : Satisfait</t>
+          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
@@ -6864,103 +6979,103 @@
       <c r="L70" s="6"/>
     </row>
     <row r="71" spans="1:12">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Eligibility badge by sector</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Met</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : Satisfait</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K71" s="9"/>
+      <c r="L71" s="6"/>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Atlantic</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your regional development agency can help you: Atlantic Canada Opportunities Agency</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence de promotion économique du Canada atlantique</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K71" s="5"/>
-      <c r="L71" s="2"/>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quebec</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your regional development agency can help you: Canada Economic Development for Quebec Regions</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les régions du Québec</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
@@ -6989,7 +7104,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -7009,12 +7124,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Northern Ontario</t>
+          <t xml:space="preserve">Your regional development agency can help you: Canada Economic Development for Quebec Regions</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Nord de l'Ontario</t>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les régions du Québec</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
@@ -7043,7 +7158,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -7063,12 +7178,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Southern Ontario</t>
+          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Northern Ontario</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Sud de l'Ontario</t>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Nord de l'Ontario</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
@@ -7097,7 +7212,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -7117,12 +7232,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your regional development agency can help you: Prairies Economic Development Canada</t>
+          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Southern Ontario</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les Prairies</t>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Sud de l'Ontario</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
@@ -7151,7 +7266,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -7171,12 +7286,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your regional development agency can help you: PacifiCan</t>
+          <t xml:space="preserve">Your regional development agency can help you: Prairies Economic Development Canada</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : PacifiCan</t>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les Prairies</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
@@ -7205,7 +7320,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -7225,12 +7340,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your regional development agency can help you: Canadian Northern Economic Development Agency</t>
+          <t xml:space="preserve">Your regional development agency can help you: PacifiCan</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence canadienne de développement économique du Nord</t>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : PacifiCan</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
@@ -7241,10 +7356,604 @@
       <c r="K77" s="5"/>
       <c r="L77" s="2"/>
     </row>
+    <row r="78" spans="1:12">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The North</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Canadian Northern Economic Development Agency</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence canadienne de développement économique du Nord</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K78" s="5"/>
+      <c r="L78" s="2"/>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Under $1 million in annual revenue</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any - sector-agnostic panel)</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is HIDDEN - not shown for this size.</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est MASQUÉ - non affiché pour cette taille.</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K79" s="9"/>
+      <c r="L79" s="6"/>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-profit, association, board of trade</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any - sector-agnostic panel)</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is HIDDEN - not shown for this size.</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est MASQUÉ - non affiché pour cette taille.</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K80" s="9"/>
+      <c r="L80" s="6"/>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any - sector-agnostic panel)</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is HIDDEN - not shown for this size.</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est MASQUÉ - non affiché pour cette taille.</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K81" s="9"/>
+      <c r="L81" s="6"/>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any - sector-agnostic panel)</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is HIDDEN - not shown for this size.</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est MASQUÉ - non affiché pour cette taille.</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K82" s="9"/>
+      <c r="L82" s="6"/>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large enterprise</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any - sector-agnostic panel)</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is SHOWN - this is the one size that reveals it.</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est AFFICHÉ - la seule taille qui le révèle.</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K83" s="9"/>
+      <c r="L83" s="6"/>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Under $1 million in annual revenue</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgriMarketing SME stream is SHOWN. AgriMarketing NIA stream is HIDDEN.</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le volet PME d'Agri-marketing est AFFICHÉ. Le volet ANI est MASQUÉ.</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K84" s="9"/>
+      <c r="L84" s="6"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-profit, association, board of trade</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgriMarketing SME stream is HIDDEN. AgriMarketing NIA stream is SHOWN - this is the one size that reveals it.</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le volet PME d'Agri-marketing est MASQUÉ. Le volet ANI est AFFICHÉ - la seule taille qui le révèle.</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K85" s="9"/>
+      <c r="L85" s="6"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgriMarketing SME stream is SHOWN. AgriMarketing NIA stream is HIDDEN.</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le volet PME d'Agri-marketing est AFFICHÉ. Le volet ANI est MASQUÉ.</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K86" s="9"/>
+      <c r="L86" s="6"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgriMarketing SME stream is SHOWN. AgriMarketing NIA stream is HIDDEN.</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le volet PME d'Agri-marketing est AFFICHÉ. Le volet ANI est MASQUÉ.</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K87" s="9"/>
+      <c r="L87" s="6"/>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large enterprise</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgriMarketing SME stream is SHOWN. AgriMarketing NIA stream is HIDDEN.</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le volet PME d'Agri-marketing est AFFICHÉ. Le volet ANI est MASQUÉ.</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K88" s="9"/>
+      <c r="L88" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L77"/>
+  <autoFilter ref="A1:L88"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J88">
       <formula1>"Open,Needs change,Approved"</formula1>
     </dataValidation>
   </dataValidations>

--- a/canada-strong/canada_strong_content_review.xlsx
+++ b/canada-strong/canada_strong_content_review.xlsx
@@ -136,7 +136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A93"/>
+  <dimension ref="A1:A112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -155,7 +155,7 @@
     <row r="3" spans="1:1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Last checked against the source files on 2026-09-03 (commit 04ebf3ee, business size).</t>
+          <t xml:space="preserve">Last checked against the source files on 2026-09-04 (commit 167c98eb).</t>
         </is>
       </c>
     </row>
@@ -197,331 +197,335 @@
       <c r="A10" s="12"/>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TAB: Decision Tree</t>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MAJOR CHANGE 2026-09-04: the whole Eligibility criteria panel (the checklist and</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Shows which selections lead to which results. The wizard has 4 questions - Need,</t>
+          <t xml:space="preserve">  its Met / Not met / Needs review badges) was removed from the tool. Those rows</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Region, Size, Sector - and the results page is built from several independent</t>
+          <t xml:space="preserve">  are gone from this tab - do not look for them. Also gone: Q4's "Exporting to the</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  blocks of content. Each block is driven by only one or two of the four questions;</t>
+          <t xml:space="preserve">  U.S. ..." answer, and the region_footnote label. New: Q1 gained a 5th answer</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the other questions do not change that block, and are marked (any).</t>
+          <t xml:space="preserve">  ("All of the above"), and two new labels (featured_prefix / featured_suffix) for</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="12"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  a Business Benefits Finder call-out. Question 2's region labels now carry</t>
+        </is>
+      </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Note: Question 2 (region) now has 7 answers, not 6 - Ontario was split into</t>
+          <t xml:space="preserve">  province/territory abbreviations and Southern Ontario was renamed "Southern and</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Northern Ontario and Southern Ontario, each its own answer with its own RDA link,</t>
+          <t xml:space="preserve">  Eastern Ontario". Question 3's size labels changed too (see that section below).</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  because FedNor and FedDev Ontario are two separate agencies. The Prairies answer</t>
-        </is>
-      </c>
+      <c r="A19" s="12"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  was also relabelled to "Manitoba, Saskatchewan, Alberta" (same region underneath).</t>
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAB: Decision Tree</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="12"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Shows which selections lead to which results. The wizard has 4 questions - Need,</t>
+        </is>
+      </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The blocks, in the order they appear on the results page:</t>
+          <t xml:space="preserve">  Region, Size, Sector - and the results page is built from several independent</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1. Sector-specific programs      - depends on Need + Sector</t>
+          <t xml:space="preserve">  blocks of content. Each block is driven by only one or two of the four questions;</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2. Sector-agnostic programs      - depends on Need only (always shown)</t>
+          <t xml:space="preserve">  the other questions do not change that block, and are marked (any).</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    3. Regional programs             - depends on Need + Region</t>
-        </is>
-      </c>
+      <c r="A25" s="12"/>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4. Sector hub links              - depends on Sector only</t>
+          <t xml:space="preserve">  The blocks, in the order they appear on the results page:</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5. Always-on hub links           - shown on every path, no matter what</t>
+          <t xml:space="preserve">    1. Sector-specific programs   - depends on Need + Sector (Size gates some lines</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    6. Eligibility - fixed criteria  - always the same, regardless of answers</t>
+          <t xml:space="preserve">                                    within a cell - see the size notes below)</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    7. Eligibility badges by size    - depends on Size (Q3) only</t>
+          <t xml:space="preserve">    2. Sector-agnostic programs   - depends on Need only (always shown)</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    8. Eligibility badge by sector   - depends on Sector (Q4) only</t>
+          <t xml:space="preserve">    3. Regional programs          - depends on Need + Region (now also Size - see</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    9. Eligibility panel - RDA note  - depends on Region (Q2) only</t>
+          <t xml:space="preserve">                                    below)</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   10. Size-gated line items         - depends on Size (Q3), layered on blocks 1 and 2 (new)</t>
+          <t xml:space="preserve">    4. Sector hub links           - depends on Sector only</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="12"/>
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    5. More options panel         - shown on every path, no matter what</t>
+        </is>
+      </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Note: as of 2026-09-03, a sector + need combination with no matching program</t>
+          <t xml:space="preserve">    6. RDA note                   - depends on Region (Q2) only</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (block 1) shows nothing at all - the old "No stream specific to your sector"</t>
+          <t xml:space="preserve">    7. "All of the above" (Q1)    - the new 5th Q1 answer, its own small block</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  notice was removed. Those rows are marked "(nothing shown here)" below.</t>
-        </is>
-      </c>
+      <c r="A36" s="12"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="12"/>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Note: block 1 - a sector + need combination with no matching program shows</t>
+        </is>
+      </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Note: block 9 - once any region is picked, a one-line note naming that region's</t>
+          <t xml:space="preserve">  nothing at all, no notice box. Those rows are marked "(nothing shown here)".</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  development agency (with a link) is appended at the bottom of the Eligibility</t>
-        </is>
-      </c>
+      <c r="A39" s="12"/>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  criteria panel, after the checklist and the Large Enterprise note. It does not</t>
+          <t xml:space="preserve">  MAJOR CHANGE 2026-09-04: size now gates far more than the 2 programs it used to</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  depend on Need, Size, or Sector.</t>
+          <t xml:space="preserve">  (LETL and AgriMarketing). Most CSV rows picked up a size restriction in this</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="12"/>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  update - BDC's Softwood Lumber Guarantee and Steel/Aluminium program, AgriStability,</t>
+        </is>
+      </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Note: Question 3 (size) now has a 5th answer, "Non-profit, association, board of</t>
+          <t xml:space="preserve">  AgriInvest, the Pivot to Grow Loan, EDC's Direct lending, and six of the seven</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  trade" - the Regional Tariff Response Initiative is open to these too. And size</t>
+          <t xml:space="preserve">  regional RTRI links (every region except Quebec) all now hide for at least one</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  can now hide or show individual programs within an already-visible panel, not</t>
+          <t xml:space="preserve">  size answer. For the Steel/Aluminium liquidity cell and every gated regional</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  just change eligibility badges: the Large Enterprise Tariff Loan only appears in</t>
+          <t xml:space="preserve">  link, picking "Under $1 million in annual revenue" hides the WHOLE panel, not</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the Liquidity panel (block 2) for "Large enterprise", and AgriMarketing's SME vs.</t>
+          <t xml:space="preserve">  just one line in it, because it was the only program in that cell. Blocks 1-3</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  National Industry Association streams in the Agriculture/Transformation panel</t>
+          <t xml:space="preserve">  now carry a Size column plus an inline note on every gated line - read those</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (block 1) switch on whether "Non-profit..." was picked. Block 1 and block 2's own</t>
+          <t xml:space="preserve">  rather than assuming Size is a background detail.</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  rows for those two panels now say so inline; block 10 spells out all 10 size x</t>
-        </is>
-      </c>
+      <c r="A50" s="12"/>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  panel combinations one at a time.</t>
+          <t xml:space="preserve">  MAJOR CHANGE 2026-09-04: the old always-on hub panel ("Where these programs are</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="12"/>
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  listed") was renamed "More options", its body text shortened, and the Business</t>
+        </is>
+      </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  To trace one full click-through: pick a Need + Sector row in block 1 (the main</t>
+          <t xml:space="preserve">  Benefits Finder was pulled out of its bullet list into its own featured</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  program panel), then read the matching Need row in block 2, the matching</t>
+          <t xml:space="preserve">  sentence at the bottom of that panel (see block 5) - departments were reading</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Need + Region row in block 3, the matching Sector row in block 4, block 5 as-is,</t>
+          <t xml:space="preserve">  the wizard's own list as the complete set of tariff programs, so the panel now</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the matching Size row in block 7, Sector row in block 8, Region row in block 9,</t>
+          <t xml:space="preserve">  points outward instead of back at itself.</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  and - if your path touches the Liquidity or Agriculture/Transformation panels -</t>
-        </is>
-      </c>
+      <c r="A57" s="12"/>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  your Size row in block 10. Together those give everything shown on that path.</t>
+          <t xml:space="preserve">  Note: block 6 (RDA note) used to sit inside the Eligibility panel; since that</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="12"/>
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  panel is gone, it is now a standalone paragraph after the More Options panel,</t>
+        </is>
+      </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Use the Comments column here to flag routing that looks wrong (a program missing</t>
+          <t xml:space="preserve">  before the Start Over link. Its label text also changed to "Get additional</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  or misplaced for a given selection), separate from wording issues in Content Review.</t>
+          <t xml:space="preserve">  support from: ". Still driven by Region (Q2) alone.</t>
         </is>
       </c>
     </row>
@@ -529,205 +533,326 @@
       <c r="A62" s="12"/>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TAB: Gap Analysis</t>
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Note: block 7 is entirely new - "All of the above" lets someone see every need's</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Compares every program named on two live Canada.ca pages - the workers/employers</t>
+          <t xml:space="preserve">  panels at once for their chosen Sector/Region/Size. It reuses blocks 1-3's</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  tariff-support page and the Canada Strong campaign page - against the CSV that</t>
+          <t xml:space="preserve">  content almost exactly; the only real differences are one deduplicated program</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  drives the wizard, to catch anything the wizard is missing.</t>
+          <t xml:space="preserve">  (Pivot to Grow Loan, filed only under Financing) and the regional panel</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1. Missing - employer/business side       - on the source page, not in the CSV</t>
+          <t xml:space="preserve">  collapsing into one combined box instead of a possible duplicate. Also note the</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2. Missing - new program (not in the CSV) - Build Communities Strong Fund</t>
+          <t xml:space="preserve">  old national RTRI hub line (used to appear in the Liquidity and Transformation</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3. Missing - worker-facing supports        - out of scope by design: the wizard</t>
+          <t xml:space="preserve">  sector-agnostic panels, block 2) was deleted outright - the per-region links in</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 only covers the business path, and</t>
+          <t xml:space="preserve">  block 3 are now the only way to reach RTRI.</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                 "I am a worker" on the start page</t>
-        </is>
-      </c>
+      <c r="A71" s="12"/>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 routes straight to that source page</t>
+          <t xml:space="preserve">  To trace one full click-through: pick a Need + Sector row in block 1, then the</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 instead of building a list</t>
+          <t xml:space="preserve">  matching Need row in block 2, the matching Need + Region row in block 3 (check</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4. Confirmed present                       - already in the wizard; Maps to</t>
+          <t xml:space="preserve">  its Size column), the matching Sector row in block 4, block 5 as-is, and the</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 wizard program names the matching</t>
+          <t xml:space="preserve">  matching Region row in block 6. If you picked "All of the above" for Need,</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 CSV / Decision Tree entry</t>
+          <t xml:space="preserve">  read block 7 instead of blocks 1-3's Need-specific rows.</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Set Status per row to Add to wizard, Won't add, or leave Open for a call still</t>
-        </is>
-      </c>
+      <c r="A77" s="12"/>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  to be made; rows already in the wizard default to Already covered.</t>
+          <t xml:space="preserve">  Use the Comments column here to flag routing that looks wrong (a program missing</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="12"/>
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  or misplaced for a given selection), separate from wording issues in Content Review.</t>
+        </is>
+      </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content Review and Decision Tree tabs: set Status to Needs change if flagging</t>
-        </is>
-      </c>
+      <c r="A80" s="12"/>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">something for a fix, or Approved once happy with a row. Leave as Open otherwise.</t>
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAB: Gap Analysis</t>
         </is>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add your name under Reviewer on any tab.</t>
+          <t xml:space="preserve">  Compares every program named on two live Canada.ca pages - the workers/employers</t>
         </is>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="12"/>
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  tariff-support page and the Canada Strong campaign page - against the CSV that</t>
+        </is>
+      </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Source files:</t>
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  drives the wizard, to catch anything the wizard is missing.</t>
         </is>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+          <t xml:space="preserve">    1. Missing - employer/business side       - on the source page, not in the CSV</t>
         </is>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+          <t xml:space="preserve">    2. Missing - new program (not in the CSV) - Build Communities Strong Fund</t>
         </is>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/tariff_tool_links.csv  (the program list behind the Decision Tree tab)</t>
+          <t xml:space="preserve">    3. Missing - worker-facing supports        - out of scope by design: the wizard</t>
         </is>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/business-en.html  (the template that assembles the results page)</t>
+          <t xml:space="preserve">                                                 only covers the business path, and</t>
         </is>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="12"/>
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 "I am a worker" on the start page</t>
+        </is>
+      </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Compared against, for the Gap Analysis tab (checked 2026-09-03):</t>
+          <t xml:space="preserve">                                                 routes straight to that source page</t>
         </is>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  https://www.canada.ca/en/department-finance/programs/international-trade-finance-policy/</t>
+          <t xml:space="preserve">                                                 instead of building a list</t>
         </is>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    canadas-response-us-tariffs/support-canadian-workers-employers.html</t>
+          <t xml:space="preserve">    4. Confirmed present                       - already in the wizard; Maps to</t>
         </is>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 wizard program names the matching</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 CSV / Decision Tree entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Set Status per row to Add to wizard, Won't add, or leave Open for a call still</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  to be made; rows already in the wizard default to Already covered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="12"/>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Content Review and Decision Tree tabs: set Status to Needs change if flagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">something for a fix, or Approved once happy with a row. Leave as Open otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add your name under Reviewer on any tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="12"/>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source files:</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/tariff_tool_links.csv  (the program list behind the Decision Tree tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/business-en.html  (the template that assembles the results page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="12"/>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Compared against, for the Gap Analysis tab (checked 2026-09-03, not re-checked in</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the 2026-09-04 rescan since neither external page changed):</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  https://www.canada.ca/en/department-finance/programs/international-trade-finance-policy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    canadas-response-us-tariffs/support-canadian-workers-employers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  https://www.canada.ca/en/campaign/canadastrong.html</t>
         </is>
@@ -739,7 +864,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1927,17 +2052,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.region_footnote</t>
+          <t xml:space="preserve">business.labels.hub_heading</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional criteria and intake dates vary.</t>
+          <t xml:space="preserve">More options</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les critères régionaux et les dates de réception des demandes varient.</t>
+          <t xml:space="preserve">Plus d'options</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -1956,17 +2081,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.hub_heading</t>
+          <t xml:space="preserve">business.labels.hub_body</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Where these programs are listed</t>
+          <t xml:space="preserve">For more programs and context:</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Où ces programmes sont répertoriés</t>
+          <t xml:space="preserve">Pour plus de programmes et de contexte :</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -1985,17 +2110,17 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.hub_body</t>
+          <t xml:space="preserve">business.labels.featured_prefix</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">These hubs are the departments' own lists. They are kept current, so check them if something here looks out of date.</t>
+          <t xml:space="preserve">Use the </t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ces carrefours sont les listes tenues par les ministères eux-mêmes. Ils sont à jour : consultez-les si une information ici semble désuète.</t>
+          <t xml:space="preserve">Utilisez l'</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -2014,17 +2139,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.rda_prefix</t>
+          <t xml:space="preserve">business.labels.featured_suffix</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your regional development agency can help you: </t>
+          <t xml:space="preserve"> to view or search all provincial and federal programs and services, including tariff support.</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : </t>
+          <t xml:space="preserve"> pour afficher ou rechercher tous les programmes et services provinciaux et fédéraux, y compris les ressources de soutien tarifaire.</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2036,53 +2161,53 @@
       <c r="G44" s="6"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business wizard - result labels</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">business.labels.rda_prefix</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get additional support from: </t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obtenez un soutien supplémentaire auprès de : </t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F45" s="9"/>
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 1 - need</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">business.questions.question-1.legend</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 1 of 4: What do you need right now?</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 1 sur 4 : De quoi avez-vous besoin en ce moment?</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F45" s="5"/>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 1 - need</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-1.option[need-fin]</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Financing to keep operating or grow</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du financement pour poursuivre vos activités ou prendre de l'expansion</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2101,17 +2226,17 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-1.option[need-liq]</t>
+          <t xml:space="preserve">question-1.option[need-fin]</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+          <t xml:space="preserve">Financing to keep operating or grow</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Des liquidités pour combler un manque de trésorerie causé par les droits de douane</t>
+          <t xml:space="preserve">Du financement pour poursuivre vos activités ou prendre de l'expansion</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -2130,17 +2255,17 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-1.option[need-tra]</t>
+          <t xml:space="preserve">question-1.option[need-liq]</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un projet de transformation ou d'immobilisations</t>
+          <t xml:space="preserve">Des liquidités pour combler un manque de trésorerie causé par les droits de douane</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -2159,17 +2284,17 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-1.option[need-wrk]</t>
+          <t xml:space="preserve">question-1.option[need-tra]</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le maintien en poste et le recyclage de votre main-d'œuvre</t>
+          <t xml:space="preserve">Un projet de transformation ou d'immobilisations</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -2181,82 +2306,82 @@
       <c r="G49" s="2"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 1 - need</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-1.option[need-wrk]</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workforce retention and retraining</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le maintien en poste et le recyclage de votre main-d'œuvre</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F50" s="5"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 1 - need</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-1.option[need-all]</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All of the above</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tout ce qui précède</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F51" s="5"/>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">business.questions.question-2.legend</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 2 of 4: Where is your business located?</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 2 sur 4 : Où votre entreprise est-elle située?</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 2 - region</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-2.option[reg-atl]</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atlantic</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atlantique</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 2 - region</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-2.option[reg-qc]</t>
-        </is>
-      </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">Question 2 of 4: Where is your business mainly located?</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Québec</t>
+          <t xml:space="preserve">Question 2 sur 4 : Où votre entreprise est-elle principalement située?</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -2275,17 +2400,17 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-on-n]</t>
+          <t xml:space="preserve">question-2.option[reg-atl]</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
+          <t xml:space="preserve">Atlantic (NB, NS, PE, NL)</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nord de l'Ontario (y compris Parry Sound)</t>
+          <t xml:space="preserve">Atlantique (NB, NS, PE, NL)</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -2304,17 +2429,17 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-on-s]</t>
+          <t xml:space="preserve">question-2.option[reg-qc]</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sud de l'Ontario (au sud de Muskoka)</t>
+          <t xml:space="preserve">Québec</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -2333,17 +2458,17 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-pr]</t>
+          <t xml:space="preserve">question-2.option[reg-on-n]</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
+          <t xml:space="preserve">Nord de l'Ontario (y compris Parry Sound)</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -2362,17 +2487,17 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-bc]</t>
+          <t xml:space="preserve">question-2.option[reg-on-s]</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Southern and Eastern Ontario</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colombie-Britannique</t>
+          <t xml:space="preserve">Sud et Est de l'Ontario</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -2391,17 +2516,17 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-nor]</t>
+          <t xml:space="preserve">question-2.option[reg-pr]</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">Prairies (MB, SK, AB)</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le Nord</t>
+          <t xml:space="preserve">Prairies (MB, SK, AB)</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -2413,82 +2538,82 @@
       <c r="G57" s="6"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 2 - region</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-2.option[reg-bc]</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">British Columbia</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colombie-Britannique</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F58" s="9"/>
+      <c r="G58" s="6"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 2 - region</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-2.option[reg-nor]</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The North (NU, NT, YT)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Nord (NU, NT, YT)</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F59" s="9"/>
+      <c r="G59" s="6"/>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 3 - size</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">business.questions.question-3.legend</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 3 of 4: What is your size and revenue?</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 3 sur 4 : Quels sont votre taille et vos revenus?</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F58" s="5"/>
-      <c r="G58" s="2"/>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 3 - size</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-3.option[size-under1m]</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Under $1 million in annual revenue</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Moins de 1 million de dollars de revenus annuels</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F59" s="5"/>
-      <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 3 - size</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-3.option[size-nonprofit]</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Non-profit, association, board of trade</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Organisme sans but lucratif, association, chambre de commerce</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -2507,17 +2632,17 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-1to5m]</t>
+          <t xml:space="preserve">question-3.option[size-under1m]</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
+          <t xml:space="preserve">Under $1 million in annual revenue</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">De 1 à 5 millions de dollars et 3 ans ou plus d'activité</t>
+          <t xml:space="preserve">Moins de 1 million de dollars de revenus annuels</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -2536,17 +2661,17 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-5mplus]</t>
+          <t xml:space="preserve">question-3.option[size-1to5m]</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
+          <t xml:space="preserve">$1 million to $5 million</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 millions de dollars ou plus et 10 employés à temps plein ou plus</t>
+          <t xml:space="preserve">De 1 à 5 millions de dollars</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -2565,17 +2690,17 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-large]</t>
+          <t xml:space="preserve">question-3.option[size-5mplus]</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Large enterprise</t>
+          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grande entreprise</t>
+          <t xml:space="preserve">5 millions de dollars ou plus et 10 employés à temps plein ou plus</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -2587,82 +2712,82 @@
       <c r="G63" s="2"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 3 - size</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-3.option[size-large]</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Larger enterprise ($150 million or more in annual revenue)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plus grande entreprise (150 millions de dollars ou plus de revenus annuels)</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F64" s="5"/>
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 3 - size</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-3.option[size-nonprofit]</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-profit, association, board of trade</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organisme sans but lucratif, association, chambre de commerce</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F65" s="5"/>
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">business.questions.question-4.legend</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 4 of 4: What is your sector and tariff impact?</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 4 sur 4 : Quel est votre secteur et quelle est l'incidence des droits de douane?</t>
-        </is>
-      </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F64" s="9"/>
-      <c r="G64" s="6"/>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 - sector</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-4.option[sec-forestry]</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forestry and softwood lumber</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Foresterie et bois d'œuvre</t>
-        </is>
-      </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F65" s="9"/>
-      <c r="G65" s="6"/>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 - sector</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-4.option[sec-steel]</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Acier, aluminium et cuivre</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -2681,17 +2806,17 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-mfg]</t>
+          <t xml:space="preserve">question-4.option[sec-forestry]</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
+          <t xml:space="preserve">Forestry and softwood lumber</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabrication et autres exportateurs</t>
+          <t xml:space="preserve">Foresterie et bois d'œuvre</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -2710,17 +2835,17 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-agri]</t>
+          <t xml:space="preserve">question-4.option[sec-steel]</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agroalimentaire, poisson et fruits de mer</t>
+          <t xml:space="preserve">Acier, aluminium et cuivre</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -2739,17 +2864,17 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-usexport]</t>
+          <t xml:space="preserve">question-4.option[sec-mfg]</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+          <t xml:space="preserve">Other manufacturing and exporters</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exportations vers les États-Unis représentant 15 % ou plus de vos revenus</t>
+          <t xml:space="preserve">Autre fabrication et exportateurs</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -2761,328 +2886,38 @@
       <c r="G69" s="6"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.eligibility.heading</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Critères d'admissibilité</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F70" s="5"/>
-      <c r="G70" s="2"/>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.eligibility.body</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Programs on this page commonly apply these criteria. This is a guide, not a decision - the program you apply to makes the final determination.</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les programmes de cette page appliquent couramment ces critères. Il s'agit d'un guide et non d'une décision : le programme auquel vous présentez une demande rend la décision finale.</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F71" s="5"/>
-      <c r="G71" s="2"/>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">criteria[0].text (incorporation)</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Canadian-incorporated</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Constituée en société au Canada</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F72" s="5"/>
-      <c r="G72" s="2"/>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">criteria[1].text (years operating)</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 or more years operating</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 ans ou plus d'activité</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F73" s="5"/>
-      <c r="G73" s="2"/>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">criteria[2].text (revenue)</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$1 million or more in annual revenue</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 million de dollars ou plus de revenus annuels</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F74" s="5"/>
-      <c r="G74" s="2"/>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">criteria[3].text (cash flow)</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Positive cash flow</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flux de trésorerie positif</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F75" s="5"/>
-      <c r="G75" s="2"/>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">criteria[4].text (US export/tariff impact)</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15% or more of revenue from U.S. exports, or a 10% tariff-driven revenue decline or cost increase</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15 % ou plus des revenus provenant d'exportations vers les États-Unis, ou une baisse de revenus ou une hausse de coûts de 10 % attribuable aux droits de douane</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F76" s="5"/>
-      <c r="G76" s="2"/>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.eligibility.large_note</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size.</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille.</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F77" s="5"/>
-      <c r="G77" s="2"/>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility badges</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badge[met] (years/revenue/US export)</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Met</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Satisfait</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F78" s="9"/>
-      <c r="G78" s="6"/>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility badges</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badge[review] (incorporation/years/cash flow/US export)</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Needs review</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">À vérifier</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F79" s="9"/>
-      <c r="G79" s="6"/>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility badges</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badge[notmet] (revenue)</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not met</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Non satisfait</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F80" s="9"/>
-      <c r="G80" s="6"/>
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 4 - sector</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-4.option[sec-agri]</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agroalimentaire, poisson et fruits de mer</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F70" s="9"/>
+      <c r="G70" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G80"/>
+  <autoFilter ref="A1:G70"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E80">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E70">
       <formula1>"Open,Needs change,Approved"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3091,18 +2926,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
-    <col min="8" max="8" width="46" customWidth="1"/>
-    <col min="9" max="9" width="46" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="9" max="9" width="50" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
@@ -3193,7 +3028,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">n/a - no programs in this cell</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3247,7 +3082,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">n/a - no programs in this cell</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -3306,7 +3141,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
+          <t xml:space="preserve">Other manufacturing and exporters</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3316,12 +3151,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - manufacturing has no sector stream; see block 2 below)</t>
+          <t xml:space="preserve">(none - this sector has no sector-specific stream; see block 2)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - la fabrication n'a pas de volet sectoriel; voir le bloc 2 ci-dessous)</t>
+          <t xml:space="preserve">(aucun - ce secteur n'a pas de volet sectoriel; voir le bloc 2)</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -3355,7 +3190,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">All sizes (no gating in this cell)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3365,7 +3200,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture and lumber: financing</t>
+          <t xml:space="preserve">Agriculture: financing</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -3401,7 +3236,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financing to keep operating or grow</t>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3411,27 +3246,29 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Mixed - see line notes</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+          <t xml:space="preserve">Forestry and softwood lumber</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no sector-specific panel)</t>
+          <t xml:space="preserve">Forestry and lumber: liquidity</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - the U.S.-exporter answer has no sector stream; see block 2 below)</t>
+          <t xml:space="preserve">Forestry Support Program - Cash Flow Support stream (BDC) - all sizes
+Softwood Lumber Guarantee Program (BDC) - shown for every size EXCEPT "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - la réponse exportateur vers les É.-U. n'a pas de volet sectoriel; voir le bloc 2 ci-dessous)</t>
+          <t xml:space="preserve">Programme de soutien à la foresterie – volet soutien aux liquidités (BDC) - toutes tailles
+Programme de garantie du bois d'œuvre résineux (BDC) - affiché pour toute taille SAUF « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -3465,29 +3302,27 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Panel HIDDEN ENTIRELY for "Under $1 million" - its one program is size-gated</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forestry and softwood lumber</t>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forestry and lumber: liquidity</t>
+          <t xml:space="preserve">Steel and aluminum: liquidity (not shown at all for "Under $1 million in annual revenue")</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forestry Support Program - Cash Flow Support stream (BDC)
-Softwood Lumber Guarantee Program (BDC)</t>
+          <t xml:space="preserve">Steel and Aluminium Industries Support Program (BDC) - shown for every size EXCEPT "Under $1 million in annual revenue"; since it is the only program in this cell, picking that size shows NO panel here at all, not an empty one</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programme de soutien à la foresterie – volet soutien aux liquidités (BDC)
-Programme de garantie du bois d'œuvre résineux (BDC)</t>
+          <t xml:space="preserve">Programme de soutien aux industries de l'acier et de l'aluminium (BDC) - affiché pour toute taille SAUF « Moins de 1 million de dollars de revenus annuels »; comme c'est le seul programme de cette case, choisir cette taille n'affiche AUCUN encadré ici, pas un encadré vide</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -3526,22 +3361,22 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
+          <t xml:space="preserve">Other manufacturing and exporters</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steel and aluminum: liquidity</t>
+          <t xml:space="preserve">(no sector-specific panel)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steel and Aluminium Industries Support Program (BDC)</t>
+          <t xml:space="preserve">(none - this sector has no sector-specific stream; see block 2)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programme de soutien aux industries de l'acier et de l'aluminium (BDC)</t>
+          <t xml:space="preserve">(aucun - ce secteur n'a pas de volet sectoriel; voir le bloc 2)</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -3575,27 +3410,35 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Mixed - see line notes</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no sector-specific panel)</t>
+          <t xml:space="preserve">Agriculture: liquidity</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - manufacturing has no sector stream; see block 2 below)</t>
+          <t xml:space="preserve">Advance Payments Program (APP) (AAFC) - all sizes
+Trade Disruption Customer Support Program (FCC / FAC) - all sizes
+AgriStability (AAFC) - shown for every size EXCEPT "Non-profit, association, board of trade" (farmers only)
+AgriInvest (AAFC) - shown for every size EXCEPT "Non-profit, association, board of trade" (farmers only)
+Price Pooling Program (AAFC) - all sizes</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - la fabrication n'a pas de volet sectoriel; voir le bloc 2 ci-dessous)</t>
+          <t xml:space="preserve">Programme de paiements anticipés (AAFC) - toutes tailles
+Programme de soutien à la clientèle en cas de perturbations commerciales (FCC / FAC) - toutes tailles
+Agri-stabilité (AAFC) - affiché pour toute taille SAUF « Organisme sans but lucratif, association, chambre de commerce » (agriculteurs seulement)
+Agri-investissement (AAFC) - affiché pour toute taille SAUF « Organisme sans but lucratif, association, chambre de commerce » (agriculteurs seulement)
+Programme de mise en commun des prix (AAFC) - toutes tailles</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -3619,7 +3462,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3629,136 +3472,20 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">All sizes (no gating in this cell)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+          <t xml:space="preserve">Forestry and softwood lumber</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture: liquidity</t>
+          <t xml:space="preserve">Forestry and lumber: transformation and capital projects</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Advance Payments Program (APP) (AAFC)
-Trade Disruption Customer Support Program (FCC / FAC)
-AgriStability (AAFC)
-AgriInvest (AAFC)
-Price Pooling Program (AAFC)</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Programme de paiements anticipés (AAFC)
-Programme de soutien à la clientèle en cas de perturbations commerciales (FCC / FAC)
-Agri-stabilité (AAFC)
-Agri-investissement (AAFC)
-Programme de mise en commun des prix (AAFC)</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Sector-specific programs</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need + Q4 Sector</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no sector-specific panel)</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(none - the U.S.-exporter answer has no sector stream; see block 2 below)</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(aucun - la réponse exportateur vers les É.-U. n'a pas de volet sectoriel; voir le bloc 2 ci-dessous)</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Sector-specific programs</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need + Q4 Sector</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transformation or capital project</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forestry and softwood lumber</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forestry and lumber: transformation and capital projects</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Investments in Forest Industry Transformation (IFIT) (NRCan)
 Forest Innovation Program (NRCan)
@@ -3766,7 +3493,7 @@
 Global Forest Leadership Program (NRCan)</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Investissements dans la transformation de l'industrie forestière (ITIF) (NRCan)
 Programme d'innovation forestière (NRCan)
@@ -3774,6 +3501,114 @@
 Programme de leadership mondial sur les forêts (NRCan)</t>
         </is>
       </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K10" s="5"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Sector-specific programs</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q4 Sector</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a - no programs in this cell</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(nothing shown here)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Sector-specific programs</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q4 Sector</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other manufacturing and exporters</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no sector-specific panel)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - this sector has no sector-specific stream; see block 2)</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - ce secteur n'a pas de volet sectoriel; voir le bloc 2)</t>
+        </is>
+      </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
@@ -3805,27 +3640,35 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">SME stream vs. NIA stream switch on the non-profit answer</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(nothing shown here)</t>
+          <t xml:space="preserve">Agriculture: transformation and capital projects</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
+          <t xml:space="preserve">AgriMarketing Program: Market Diversification for SMEs (AAFC) - shown for every size EXCEPT "Non-profit, association, board of trade"
+AgriMarketing Program: Market Diversification for National Industry Associations (AAFC) - shown ONLY for "Non-profit, association, board of trade"
+Trade Commissioner Service (agri-food) (AAFC) - all sizes
+Canada Brand (AAFC) - all sizes
+Single window contact for agri-food trade services (AAFC) - all sizes</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
+          <t xml:space="preserve">Programme Agri-marketing : Diversification des marchés pour les petites et moyennes entreprises (AAFC) - affiché pour toute taille SAUF « Organisme sans but lucratif, association, chambre de commerce »
+Programme Agri-marketing : Diversification des marchés pour les associations nationales de l'industrie (AAFC) - affiché UNIQUEMENT pour « Organisme sans but lucratif, association, chambre de commerce »
+Service des délégués commerciaux (AAFC) - toutes tailles
+Marque Canada (AAFC) - toutes tailles
+Guichet unique pour communiquer avec le Service d'exportation agroalimentaire (AAFC) - toutes tailles</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -3849,7 +3692,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Workforce retention and retraining</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3859,27 +3702,27 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">n/a - no programs in this cell</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
+          <t xml:space="preserve">Forestry and softwood lumber</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no sector-specific panel)</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - manufacturing has no sector stream; see block 2 below)</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - la fabrication n'a pas de volet sectoriel; voir le bloc 2 ci-dessous)</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -3898,12 +3741,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1 Need + Q4 Sector (2 lines also gated by Q3 Size - see block 10)</t>
+          <t xml:space="preserve">Q1 Need + Q4 Sector</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Workforce retention and retraining</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3913,35 +3756,27 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any - 2 of these 5 lines are size-gated, see block 10)</t>
+          <t xml:space="preserve">n/a - no programs in this cell</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture: transformation and capital projects</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AgriMarketing Program: Market Diversification for SMEs (AAFC) - shown for every Q3 answer EXCEPT "Non-profit, association, board of trade"
-AgriMarketing Program: Market Diversification for National Industry Associations (AAFC) - shown ONLY for "Non-profit, association, board of trade"
-Trade Commissioner Service (agri-food) (AAFC)
-Canada Brand (AAFC)
-Single window contact for agri-food trade services (AAFC)</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programme Agri-marketing : Diversification des marchés pour les petites et moyennes entreprises (AAFC) - affiché pour toute réponse Q3 SAUF « Organisme sans but lucratif, association, chambre de commerce »
-Programme Agri-marketing : Diversification des marchés pour les associations nationales de l'industrie (AAFC) - affiché UNIQUEMENT pour « Organisme sans but lucratif, association, chambre de commerce »
-Service des délégués commerciaux (AAFC)
-Marque Canada (AAFC)
-Guichet unique pour communiquer avec le Service d'exportation agroalimentaire (AAFC)</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -3965,7 +3800,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Workforce retention and retraining</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3980,7 +3815,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+          <t xml:space="preserve">Other manufacturing and exporters</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3990,12 +3825,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - the U.S.-exporter answer has no sector stream; see block 2 below)</t>
+          <t xml:space="preserve">(none - this sector has no sector-specific stream; see block 2)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - la réponse exportateur vers les É.-U. n'a pas de volet sectoriel; voir le bloc 2 ci-dessous)</t>
+          <t xml:space="preserve">(aucun - ce secteur n'a pas de volet sectoriel; voir le bloc 2)</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -4029,12 +3864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">n/a - no programs in this cell</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forestry and softwood lumber</t>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4061,442 +3896,226 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Sector-specific programs</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need + Q4 Sector</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Sector-agnostic programs</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need only (always shown)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financing to keep operating or grow</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixed - see line notes</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financing: open to all sectors</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipment Loan (BDC) - all sizes
+Working Capital Guarantees (EDC) - all sizes
+Pivot to Grow Loan (BDC) - shown for every size EXCEPT "Under $1 million in annual revenue"
+Direct lending (EDC) - shown ONLY for "$5 million or more with 10 or more full-time employees" and "Larger enterprise"</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prêt pour équipement (BDC) - toutes tailles
+Garanties de fonds de roulement (EDC) - toutes tailles
+Prêt Pivoter pour se propulser (BDC) - affiché pour toute taille SAUF « Moins de 1 million de dollars de revenus annuels »
+Prêts directs (EDC) - affiché UNIQUEMENT pour « 5 millions de dollars ou plus... » et « Plus grande entreprise »</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K18" s="9"/>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Sector-agnostic programs</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need only (always shown)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixed - see line notes</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity: open to all sectors</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duties Relief Program (CBSA) - all sizes
+Duty Drawback Program (CBSA) - all sizes
+Process for requesting remission of tariffs (Finance Canada) - all sizes
+Pivot to Grow Loan (BDC) - shown for every size EXCEPT "Under $1 million in annual revenue"
+Large Enterprise Tariff Loan (LETL) (CEEFC / CDEV) - shown ONLY for "Larger enterprise"
+(the old "Regional Tariff Response Initiative (national hub)" line was removed as of this update - see block 3 for the per-region version, now the only RTRI entry point)</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme d'exonération des droits (CBSA) - toutes tailles
+Programme de drawback (CBSA) - toutes tailles
+Processus de demande de remise des droits de douane (Finance Canada) - toutes tailles
+Prêt Pivoter pour se propulser (BDC) - affiché pour toute taille SAUF « Moins de 1 million de dollars de revenus annuels »
+Crédit pour les grandes entreprises touchées par les droits de douane (CGETDD) (CEEFC / CDEV) - affiché UNIQUEMENT pour « Plus grande entreprise »
+(l'ancienne ligne « Initiative régionale de réponse tarifaire (national hub) » a été retirée lors de cette mise à jour - voir le bloc 3 pour la version régionale, désormais le seul point d'entrée de l'IRRT)</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K19" s="9"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Sector-agnostic programs</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need only (always shown)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All sizes (no gating in this cell)</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation and capital projects: open to all sectors</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strategic Response Fund (SRF) (ISED)
+Market diversification guide (EDC)
+TCS - US tariffs support for exporters (GAC)
+(the old "Regional Tariff Response Initiative (national hub)" line was removed as of this update - see block 3)</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fonds de réponse stratégique (FRS) (ISED)
+Diversification des marchés (EDC)
+Soutien pour les exportateurs canadiens face aux droits de douane imposés par les États-Unis (GAC)
+(l'ancienne ligne « Initiative régionale de réponse tarifaire (national hub) » a été retirée lors de cette mise à jour - voir le bloc 3)</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K20" s="9"/>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Sector-agnostic programs</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need only (always shown)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Workforce retention and retraining</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(nothing shown here)</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K18" s="5"/>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Sector-specific programs</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need + Q4 Sector</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no sector-specific panel)</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(none - manufacturing has no sector stream; see block 2 below)</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(aucun - la fabrication n'a pas de volet sectoriel; voir le bloc 2 ci-dessous)</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Sector-specific programs</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need + Q4 Sector</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(nothing shown here)</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K20" s="5"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Sector-specific programs</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need + Q4 Sector</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no sector-specific panel)</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(none - the U.S.-exporter answer has no sector stream; see block 2 below)</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(aucun - la réponse exportateur vers les É.-U. n'a pas de volet sectoriel; voir le bloc 2 ci-dessous)</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K21" s="5"/>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. Sector-agnostic programs</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need only (always shown)</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Financing to keep operating or grow</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Financing: open to all sectors</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pivot to Grow Loan (BDC)
-Equipment Loan (BDC)
-Working Capital Guarantees (EDC)
-Financing solutions (EDC)</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prêt Pivoter pour se propulser (BDC)
-Prêt pour équipement (BDC)
-Garanties de fonds de roulement (EDC)
-Prêts pour les exportateurs et les acheteurs (EDC)</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K22" s="9"/>
-      <c r="L22" s="6"/>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. Sector-agnostic programs</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need only (1 line also gated by Q3 Size - see block 10)</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any - 1 of these 6 lines is size-gated, see block 10)</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity: open to all sectors</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pivot to Grow Loan - Liquidity Support stream (BDC)
-Large Enterprise Tariff Loan (LETL) (CEEFC / CDEV) - shown ONLY for "Large enterprise"
-Regional Tariff Response Initiative (national hub) (ISED / RDAs)
-Duties Relief Program (CBSA)
-Duty Drawback Program (CBSA)
-Process for requesting remission of tariffs (Finance Canada)</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prêt Pivoter pour se propulser – volet soutien aux liquidités (BDC)
-Crédit pour les grandes entreprises touchées par les droits de douane (CGETDD) (CEEFC / CDEV) - affiché UNIQUEMENT pour « Grande entreprise »
-Initiative régionale de réponse tarifaire (ISED / RDAs)
-Programme d'exonération des droits (CBSA)
-Programme de drawback (CBSA)
-Processus de demande de remise des droits de douane (Finance Canada)</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="6"/>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. Sector-agnostic programs</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need only (always shown)</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transformation or capital project</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transformation and capital projects: open to all sectors</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Strategic Response Fund (SRF) (ISED)
-Regional Tariff Response Initiative (national hub) (ISED / RDAs)
-Market diversification guide (EDC)
-TCS - US tariffs support for exporters (GAC)</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fonds de réponse stratégique (FRS) (ISED)
-Initiative régionale de réponse tarifaire (ISED / RDAs)
-Diversification des marchés (EDC)
-Soutien pour les exportateurs canadiens face aux droits de douane imposés par les États-Unis (GAC)</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K24" s="9"/>
-      <c r="L24" s="6"/>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. Sector-agnostic programs</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need only (always shown)</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All sizes (no gating in this cell)</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Workforce retention and retraining: open to all sectors</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Worker Retention Grant (ESDC)
 Workforce Tariff Response - EI-funded LMDAs (ESDC)
@@ -4504,7 +4123,7 @@
 Student Work Placement Program (ESDC)</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Subvention pour le maintien à l'emploi des travailleurs (ESDC)
 Réponse tarifaire pour la main-d'œuvre (ESDC)
@@ -4512,16 +4131,232 @@
 Programme de stages pratiques pour étudiants (ESDC)</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="6"/>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K21" s="9"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Regional programs</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q2 Region</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financing to keep operating or grow</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atlantic (NB, NS, PE, NL)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no regional panel)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - financing has no region-specific program)</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - le financement n'a pas de programme régional)</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K22" s="5"/>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Regional programs</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q2 Region</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financing to keep operating or grow</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quebec</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no regional panel)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - financing has no region-specific program)</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - le financement n'a pas de programme régional)</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K23" s="5"/>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Regional programs</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q2 Region</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financing to keep operating or grow</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no regional panel)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - financing has no region-specific program)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - le financement n'a pas de programme régional)</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K24" s="5"/>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Regional programs</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q2 Region</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financing to keep operating or grow</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Southern and Eastern Ontario</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no regional panel)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - financing has no region-specific program)</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - le financement n'a pas de programme régional)</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K25" s="5"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Regional programs</t>
         </is>
@@ -4538,7 +4373,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantic</t>
+          <t xml:space="preserve">Prairies (MB, SK, AB)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -4592,7 +4427,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -4646,7 +4481,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
+          <t xml:space="preserve">The North (NU, NT, YT)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -4695,17 +4530,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financing to keep operating or grow</t>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
+          <t xml:space="preserve">Atlantic (NB, NS, PE, NL)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size EXCEPT "Under $1 million"</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -4715,17 +4550,17 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no regional panel)</t>
+          <t xml:space="preserve">Programs for your region</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - financing has no region-specific program)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Atlantic (ACOA / APECA) - hidden entirely for "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - le financement n'a pas de programme régional)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire au Canada atlantique (ACOA / APECA) - masqué entièrement pour « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -4749,17 +4584,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financing to keep operating or grow</t>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size - no restriction</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4769,17 +4604,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no regional panel)</t>
+          <t xml:space="preserve">Programs for your region</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - financing has no region-specific program)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Quebec (CED / DEC) - the one region with no size gate at all</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - le financement n'a pas de programme régional)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Québec (CED / DEC) - la seule région sans restriction de taille</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -4803,17 +4638,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financing to keep operating or grow</t>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size EXCEPT "Under $1 million"</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4823,17 +4658,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no regional panel)</t>
+          <t xml:space="preserve">Programs for your region</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - financing has no region-specific program)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Northern Ontario (FedNor) - hidden entirely for "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - le financement n'a pas de programme régional)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord de l'Ontario (FedNor) - masqué entièrement pour « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -4857,17 +4692,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financing to keep operating or grow</t>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">Southern and Eastern Ontario</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size EXCEPT "Under $1 million"</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4877,17 +4712,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no regional panel)</t>
+          <t xml:space="preserve">Programs for your region</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - financing has no region-specific program)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Southern Ontario (FedDev Ontario) - hidden entirely for "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - le financement n'a pas de programme régional)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire dans le Sud de l'Ontario (FedDev Ontario) - masqué entièrement pour « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -4916,12 +4751,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantic</t>
+          <t xml:space="preserve">Prairies (MB, SK, AB)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size EXCEPT "Under $1 million"</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4936,12 +4771,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Atlantic (ACOA / APECA)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Prairies (PrairiesCan) - hidden entirely for "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire au Canada atlantique (ACOA / APECA)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire (IRRT) pour la région des Prairies (PrairiesCan) - masqué entièrement pour « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -4970,12 +4805,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size EXCEPT "Under $1 million"</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4990,12 +4825,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Quebec (CED / DEC)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - British Columbia (PacifiCan) - hidden entirely for "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Québec (CED / DEC)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire en Colombie-Britannique (PacifiCan) - masqué entièrement pour « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -5024,12 +4859,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
+          <t xml:space="preserve">The North (NU, NT, YT)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size EXCEPT "Under $1 million"</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -5044,12 +4879,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Northern Ontario (FedNor)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - North (CanNor) - hidden entirely for "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord de l'Ontario (FedNor)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord (CanNor) - masqué entièrement pour « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -5073,17 +4908,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
+          <t xml:space="preserve">Atlantic (NB, NS, PE, NL)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size EXCEPT "Under $1 million"</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -5098,12 +4933,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Southern Ontario (FedDev Ontario)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Atlantic (ACOA / APECA) - hidden entirely for "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire dans le Sud de l'Ontario (FedDev Ontario)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire au Canada atlantique (ACOA / APECA) - masqué entièrement pour « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -5127,17 +4962,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size - no restriction</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -5152,12 +4987,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Prairies (PrairiesCan)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Quebec (CED / DEC) - the one region with no size gate at all</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire (IRRT) pour la région des Prairies (PrairiesCan)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Québec (CED / DEC) - la seule région sans restriction de taille</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -5181,17 +5016,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size EXCEPT "Under $1 million"</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5206,12 +5041,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - British Columbia (PacifiCan)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Northern Ontario (FedNor) - hidden entirely for "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire en Colombie-Britannique (PacifiCan)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord de l'Ontario (FedNor) - masqué entièrement pour « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -5235,17 +5070,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">Southern and Eastern Ontario</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size EXCEPT "Under $1 million"</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5260,12 +5095,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - North (CanNor)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Southern Ontario (FedDev Ontario) - hidden entirely for "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord (CanNor)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire dans le Sud de l'Ontario (FedDev Ontario) - masqué entièrement pour « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -5294,12 +5129,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantic</t>
+          <t xml:space="preserve">Prairies (MB, SK, AB)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size EXCEPT "Under $1 million"</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5314,12 +5149,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Atlantic (ACOA / APECA)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Prairies (PrairiesCan) - hidden entirely for "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire au Canada atlantique (ACOA / APECA)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire (IRRT) pour la région des Prairies (PrairiesCan) - masqué entièrement pour « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -5348,12 +5183,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size EXCEPT "Under $1 million"</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5368,12 +5203,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Quebec (CED / DEC)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - British Columbia (PacifiCan) - hidden entirely for "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Québec (CED / DEC)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire en Colombie-Britannique (PacifiCan) - masqué entièrement pour « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -5402,12 +5237,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
+          <t xml:space="preserve">The North (NU, NT, YT)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Shown for every size EXCEPT "Under $1 million"</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5422,12 +5257,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Northern Ontario (FedNor)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - North (CanNor) - hidden entirely for "Under $1 million in annual revenue"</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord de l'Ontario (FedNor)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord (CanNor) - masqué entièrement pour « Moins de 1 million de dollars de revenus annuels »</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -5451,12 +5286,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Workforce retention and retraining</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
+          <t xml:space="preserve">Atlantic (NB, NS, PE, NL)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5471,17 +5306,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programs for your region</t>
+          <t xml:space="preserve">(no regional panel)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Southern Ontario (FedDev Ontario)</t>
+          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire dans le Sud de l'Ontario (FedDev Ontario)</t>
+          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -5505,12 +5340,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Workforce retention and retraining</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5525,17 +5360,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programs for your region</t>
+          <t xml:space="preserve">(no regional panel)</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Prairies (PrairiesCan)</t>
+          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire (IRRT) pour la région des Prairies (PrairiesCan)</t>
+          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -5559,12 +5394,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Workforce retention and retraining</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5579,17 +5414,17 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programs for your region</t>
+          <t xml:space="preserve">(no regional panel)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - British Columbia (PacifiCan)</t>
+          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire en Colombie-Britannique (PacifiCan)</t>
+          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -5613,12 +5448,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Workforce retention and retraining</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">Southern and Eastern Ontario</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5633,17 +5468,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programs for your region</t>
+          <t xml:space="preserve">(no regional panel)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - North (CanNor)</t>
+          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord (CanNor)</t>
+          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -5672,7 +5507,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantic</t>
+          <t xml:space="preserve">Prairies (MB, SK, AB)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5726,7 +5561,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5780,7 +5615,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
+          <t xml:space="preserve">The North (NU, NT, YT)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5817,338 +5652,344 @@
       <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. Regional programs</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need + Q2 Region</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no regional panel)</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K50" s="5"/>
-      <c r="L50" s="2"/>
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Sector hub links</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forestry and softwood lumber</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forestry and lumber: where these programs are listed</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support for forest sector employers and workers (hub) (NRCan)</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soutien fédéral aux entreprises et aux travailleurs du secteur forestier (NRCan)</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K50" s="9"/>
+      <c r="L50" s="6"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. Regional programs</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need + Q2 Region</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no regional panel)</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K51" s="5"/>
-      <c r="L51" s="2"/>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Sector hub links</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Steel and aluminum: where these programs are listed</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support for the Canadian steel sector (Finance Canada)</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soutien au secteur canadien de l'acier (Finance Canada)</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K51" s="9"/>
+      <c r="L51" s="6"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. Regional programs</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need + Q2 Region</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">British Columbia</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no regional panel)</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K52" s="5"/>
-      <c r="L52" s="2"/>
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Sector hub links</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other manufacturing and exporters</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no sector hub)</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none)</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun)</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K52" s="9"/>
+      <c r="L52" s="6"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. Regional programs</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 Need + Q2 Region</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The North</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no regional panel)</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K53" s="5"/>
-      <c r="L53" s="2"/>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Sector hub links</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture: where these programs are listed</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgPal / AgriGuichet (AAFC, third-party hosted)
+Support measures for industries affected by trade disruptions (hub) (AAFC)</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgriGuichet (AAFC, hébergé par un tiers)
+Mesures de soutien pour les industries touchées par les perturbations commerciales (AAFC)</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K53" s="9"/>
+      <c r="L53" s="6"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4. Sector hub links</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forestry and softwood lumber</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forestry and lumber: where these programs are listed</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support for forest sector employers and workers (hub) (NRCan)</t>
-        </is>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Soutien fédéral aux entreprises et aux travailleurs du secteur forestier (NRCan)</t>
-        </is>
-      </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K54" s="9"/>
-      <c r="L54" s="6"/>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. More options panel (renamed from "Where these programs are listed")</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None - shown on every path</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More options</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supports for business (hub) (ISED)
+Support for Canadian workers and employers (Finance Canada)
+(Business Benefits Finder moved OUT of this list - it is now the separate featured line below, not a bullet here)</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soutien aux entreprises (ISED)
+Soutien aux employeurs et aux travailleurs canadiens en réponse aux droits de douane (Finance Canada)
+(l'Outil de recherche d'aide aux entreprises est sorti de cette liste - c'est maintenant la ligne en vedette séparée ci-dessous, plus une puce ici)</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K54" s="5"/>
+      <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4. Sector hub links</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Steel and aluminum: where these programs are listed</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support for the Canadian steel sector (Finance Canada)</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Soutien au secteur canadien de l'acier (Finance Canada)</t>
-        </is>
-      </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K55" s="9"/>
-      <c r="L55" s="6"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. More options panel (renamed from "Where these programs are listed")</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None - shown on every path</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More options (featured line, no org shown)</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use the Business Benefits Finder to view or search all provincial and federal programs and services, including tariff support.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Utilisez l'Outil de recherche d'aide aux entreprises pour afficher ou rechercher tous les programmes et services provinciaux et fédéraux, y compris les ressources de soutien tarifaire.</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K55" s="5"/>
+      <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4. Sector hub links</t>
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Regional development agency note</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -6158,7 +5999,7 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Atlantic (NB, NS, PE, NL)</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -6168,22 +6009,22 @@
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
+          <t xml:space="preserve">(any)</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no sector hub)</t>
+          <t xml:space="preserve">Standalone paragraph after the More Options panel (eligibility panel it used to sit in is gone)</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none)</t>
+          <t xml:space="preserve">Get additional support from: Atlantic Canada Opportunities Agency</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun)</t>
+          <t xml:space="preserve">Obtenez un soutien supplémentaire auprès de : Agence de promotion économique du Canada atlantique</t>
         </is>
       </c>
       <c r="J56" s="9" t="inlineStr">
@@ -6197,12 +6038,12 @@
     <row r="57" spans="1:12">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. Sector hub links</t>
+          <t xml:space="preserve">6. Regional development agency note</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -6212,7 +6053,7 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -6222,24 +6063,22 @@
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+          <t xml:space="preserve">(any)</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture: where these programs are listed</t>
+          <t xml:space="preserve">Standalone paragraph after the More Options panel (eligibility panel it used to sit in is gone)</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AgPal / AgriGuichet (AAFC, third-party hosted)
-Support measures for industries affected by trade disruptions (hub) (AAFC)</t>
+          <t xml:space="preserve">Get additional support from: Canada Economic Development for Quebec Regions</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AgriGuichet (AAFC, hébergé par un tiers)
-Mesures de soutien pour les industries touchées par les perturbations commerciales (AAFC)</t>
+          <t xml:space="preserve">Obtenez un soutien supplémentaire auprès de : Développement économique Canada pour les régions du Québec</t>
         </is>
       </c>
       <c r="J57" s="9" t="inlineStr">
@@ -6253,12 +6092,12 @@
     <row r="58" spans="1:12">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. Sector hub links</t>
+          <t xml:space="preserve">6. Regional development agency note</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -6268,7 +6107,7 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -6278,22 +6117,22 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+          <t xml:space="preserve">(any)</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no sector hub)</t>
+          <t xml:space="preserve">Standalone paragraph after the More Options panel (eligibility panel it used to sit in is gone)</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none)</t>
+          <t xml:space="preserve">Get additional support from: Federal Economic Development Agency for Northern Ontario</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun)</t>
+          <t xml:space="preserve">Obtenez un soutien supplémentaire auprès de : Agence fédérale de développement économique pour le Nord de l'Ontario</t>
         </is>
       </c>
       <c r="J58" s="9" t="inlineStr">
@@ -6305,72 +6144,68 @@
       <c r="L58" s="6"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5. Always-on hub links</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None - shown on every path</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Where these programs are listed</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Business Benefits Finder (ISED)
-Supports for business (hub) (ISED)
-Support for Canadian workers and employers (Finance Canada)</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Outil de recherche d'aide aux entreprises (ISED)
-Soutien aux entreprises (ISED)
-Soutien aux employeurs et aux travailleurs canadiens en réponse aux droits de douane (Finance Canada)</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K59" s="5"/>
-      <c r="L59" s="2"/>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Regional development agency note</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Southern and Eastern Ontario</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standalone paragraph after the More Options panel (eligibility panel it used to sit in is gone)</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get additional support from: Federal Economic Development Agency for Southern Ontario</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obtenez un soutien supplémentaire auprès de : Agence fédérale de développement économique pour le Sud de l'Ontario</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K59" s="9"/>
+      <c r="L59" s="6"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6. Eligibility - fixed criteria</t>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Regional development agency note</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">None - always the same badge</t>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -6380,7 +6215,7 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Prairies (MB, SK, AB)</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -6395,17 +6230,17 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility criteria</t>
+          <t xml:space="preserve">Standalone paragraph after the More Options panel (eligibility panel it used to sit in is gone)</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Canadian-incorporated" badge: Needs review</t>
+          <t xml:space="preserve">Get additional support from: Prairies Economic Development Canada</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insigne pour « Constituée en société au Canada » : À vérifier</t>
+          <t xml:space="preserve">Obtenez un soutien supplémentaire auprès de : Développement économique Canada pour les Prairies</t>
         </is>
       </c>
       <c r="J60" s="9" t="inlineStr">
@@ -6419,12 +6254,12 @@
     <row r="61" spans="1:12">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">6. Eligibility - fixed criteria</t>
+          <t xml:space="preserve">6. Regional development agency note</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">None - always the same badge</t>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -6434,7 +6269,7 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -6449,17 +6284,17 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility criteria</t>
+          <t xml:space="preserve">Standalone paragraph after the More Options panel (eligibility panel it used to sit in is gone)</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Positive cash flow" badge: Needs review</t>
+          <t xml:space="preserve">Get additional support from: PacifiCan</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insigne pour « Flux de trésorerie positif » : À vérifier</t>
+          <t xml:space="preserve">Obtenez un soutien supplémentaire auprès de : PacifiCan</t>
         </is>
       </c>
       <c r="J61" s="9" t="inlineStr">
@@ -6471,77 +6306,73 @@
       <c r="L61" s="6"/>
     </row>
     <row r="62" spans="1:12">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7. Eligibility badges by size</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 Size only</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Under $1 million in annual revenue</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"3 or more years operating" badge: Needs review
-"$1 million or more in annual revenue" badge: Not met
-Large Enterprise (LETL) note: not shown</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
-Insigne pour « 1 million de dollars ou plus de revenus annuels » : Non satisfait
-Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
-        </is>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K62" s="5"/>
-      <c r="L62" s="2"/>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Regional development agency note</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The North (NU, NT, YT)</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standalone paragraph after the More Options panel (eligibility panel it used to sit in is gone)</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get additional support from: Canadian Northern Economic Development Agency</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obtenez un soutien supplémentaire auprès de : Agence canadienne de développement économique du Nord</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K62" s="9"/>
+      <c r="L62" s="6"/>
     </row>
     <row r="63" spans="1:12">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7. Eligibility badges by size</t>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7. "All of the above" (Q1's 5th answer, new)</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3 Size only</t>
+          <t xml:space="preserve">Q1 Need = All of the above only</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">All of the above</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -6551,7 +6382,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non-profit, association, board of trade</t>
+          <t xml:space="preserve">(any)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -6561,23 +6392,17 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility criteria</t>
+          <t xml:space="preserve">General mechanism</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">"3 or more years operating" badge: Needs review
-"$1 million or more in annual revenue" badge: Not met
-Large Enterprise (LETL) note: not shown
-(badges borrow size-under1m's as a placeholder - no non-profit-specific guidance yet)</t>
+          <t xml:space="preserve">Reveals a parallel set of panels, one per real need (Financing / Liquidity / Transformation / Workforce), for whichever Sector and Region/Size you also picked. For every program that lists only ONE need in the CSV (nearly all of them), this looks exactly like turning on all four needs' panels from blocks 1-3 at once - nothing new to compute.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
-Insigne pour « 1 million de dollars ou plus de revenus annuels » : Non satisfait
-Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée
-(les insignes empruntent ceux de size-under1m comme choix provisoire - aucune orientation propre aux OSBL pour le moment)</t>
+          <t xml:space="preserve">Révèle un ensemble parallèle de panneaux, un par besoin réel (Financement / Liquidités / Transformation / Main-d'œuvre), pour le secteur et la région/taille également choisis. Pour tout programme qui n'indique qu'UN SEUL besoin dans le CSV (presque tous), cela revient exactement à activer les quatre panneaux de besoins des blocs 1 à 3 en même temps - rien de nouveau à calculer.</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
@@ -6591,17 +6416,17 @@
     <row r="64" spans="1:12">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7. Eligibility badges by size</t>
+          <t xml:space="preserve">7. "All of the above" (Q1's 5th answer, new)</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3 Size only</t>
+          <t xml:space="preserve">Q1 Need = All of the above only</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">All of the above</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -6611,31 +6436,27 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
+          <t xml:space="preserve">Every size except "Under $1 million" (same gate as when Financing or Liquidity is picked alone)</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">(any - sector-agnostic panel)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility criteria</t>
+          <t xml:space="preserve">The one real dedup case: Pivot to Grow Loan</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">"3 or more years operating" badge: Met
-"$1 million or more in annual revenue" badge: Met
-Large Enterprise (LETL) note: not shown</t>
+          <t xml:space="preserve">Pivot to Grow Loan (BDC) lists need="financing;liquidity" in the CSV - the ONLY multi-need program in the whole sheet. Picked individually, it shows in BOTH the Financing-agnostic and Liquidity-agnostic panels (blocks 2). Under "All of the above" it is deduplicated and appears ONLY under the Financing heading, because Financing is listed first in its CSV need cell. It does not also appear under Liquidity here.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : Satisfait
-Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
-Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
+          <t xml:space="preserve">Le Prêt Pivoter pour se propulser (BDC) indique need="financing;liquidity" dans le CSV - le SEUL programme à plusieurs besoins de toute la feuille. Choisi individuellement, il apparaît à la fois dans les panneaux Financement-agnostique et Liquidités-agnostique (bloc 2). Sous « Tout ce qui précède », il est dédupliqué et n'apparaît QUE sous le titre Financement, car Financement est nommé en premier dans sa cellule need du CSV. Il n'apparaît pas aussi sous Liquidités ici.</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
@@ -6649,27 +6470,27 @@
     <row r="65" spans="1:12">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7. Eligibility badges by size</t>
+          <t xml:space="preserve">7. "All of the above" (Q1's 5th answer, new)</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3 Size only</t>
+          <t xml:space="preserve">Q1 Need = All of the above only</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">All of the above</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">Any region</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
+          <t xml:space="preserve">Same size gate as block 3 (every region except Quebec hides for "Under $1 million")</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -6679,21 +6500,17 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility criteria</t>
+          <t xml:space="preserve">Regional programs collapse into ONE combined panel</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">"3 or more years operating" badge: Needs review
-"$1 million or more in annual revenue" badge: Met
-Large Enterprise (LETL) note: not shown</t>
+          <t xml:space="preserve">Under any single need, at most one regional panel could ever show. Under "All of the above", Liquidity and Transformation would otherwise each try to show their own copy of the same regional program, reading as a duplicate. The template collapses these into a single "Programs for your region" panel (heading names no need) instead of two identical-looking boxes. Content and size-gating are otherwise identical to block 3's region rows.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
-Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
-Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
+          <t xml:space="preserve">Sous un seul besoin, au plus un panneau régional pouvait s'afficher. Sous « Tout ce qui précède », Liquidités et Transformation afficheraient chacun leur propre copie du même programme régional, ce qui se lirait comme un doublon. Le gabarit fusionne cela en un seul panneau « Programmes pour votre région » (le titre ne nomme aucun besoin) plutôt que deux encadrés identiques. Le contenu et la restriction de taille sont par ailleurs identiques aux lignes de région du bloc 3.</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
@@ -6704,1256 +6521,10 @@
       <c r="K65" s="5"/>
       <c r="L65" s="2"/>
     </row>
-    <row r="66" spans="1:12">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7. Eligibility badges by size</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 Size only</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Large enterprise</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"3 or more years operating" badge: Needs review
-"$1 million or more in annual revenue" badge: Met
-Large Enterprise (LETL) note: SHOWN - "As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size."</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
-Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
-Note sur le Crédit pour les grandes entreprises (CGETDD) : AFFICHÉE - « En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille. »</t>
-        </is>
-      </c>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K66" s="5"/>
-      <c r="L66" s="2"/>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forestry and softwood lumber</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
-        </is>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J67" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K67" s="9"/>
-      <c r="L67" s="6"/>
-    </row>
-    <row r="68" spans="1:12">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
-        </is>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J68" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K68" s="9"/>
-      <c r="L68" s="6"/>
-    </row>
-    <row r="69" spans="1:12">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
-        </is>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J69" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K69" s="9"/>
-      <c r="L69" s="6"/>
-    </row>
-    <row r="70" spans="1:12">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
-        </is>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K70" s="9"/>
-      <c r="L70" s="6"/>
-    </row>
-    <row r="71" spans="1:12">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Met</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : Satisfait</t>
-        </is>
-      </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K71" s="9"/>
-      <c r="L71" s="6"/>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atlantic</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your regional development agency can help you: Atlantic Canada Opportunities Agency</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence de promotion économique du Canada atlantique</t>
-        </is>
-      </c>
-      <c r="J72" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K72" s="5"/>
-      <c r="L72" s="2"/>
-    </row>
-    <row r="73" spans="1:12">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quebec</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your regional development agency can help you: Canada Economic Development for Quebec Regions</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les régions du Québec</t>
-        </is>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K73" s="5"/>
-      <c r="L73" s="2"/>
-    </row>
-    <row r="74" spans="1:12">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Northern Ontario</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Nord de l'Ontario</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K74" s="5"/>
-      <c r="L74" s="2"/>
-    </row>
-    <row r="75" spans="1:12">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Southern Ontario</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Sud de l'Ontario</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K75" s="5"/>
-      <c r="L75" s="2"/>
-    </row>
-    <row r="76" spans="1:12">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your regional development agency can help you: Prairies Economic Development Canada</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les Prairies</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K76" s="5"/>
-      <c r="L76" s="2"/>
-    </row>
-    <row r="77" spans="1:12">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">British Columbia</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your regional development agency can help you: PacifiCan</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : PacifiCan</t>
-        </is>
-      </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K77" s="5"/>
-      <c r="L77" s="2"/>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The North</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your regional development agency can help you: Canadian Northern Economic Development Agency</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence canadienne de développement économique du Nord</t>
-        </is>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K78" s="5"/>
-      <c r="L78" s="2"/>
-    </row>
-    <row r="79" spans="1:12">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Under $1 million in annual revenue</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any - sector-agnostic panel)</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
-        </is>
-      </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is HIDDEN - not shown for this size.</t>
-        </is>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est MASQUÉ - non affiché pour cette taille.</t>
-        </is>
-      </c>
-      <c r="J79" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K79" s="9"/>
-      <c r="L79" s="6"/>
-    </row>
-    <row r="80" spans="1:12">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Non-profit, association, board of trade</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any - sector-agnostic panel)</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is HIDDEN - not shown for this size.</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est MASQUÉ - non affiché pour cette taille.</t>
-        </is>
-      </c>
-      <c r="J80" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K80" s="9"/>
-      <c r="L80" s="6"/>
-    </row>
-    <row r="81" spans="1:12">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any - sector-agnostic panel)</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is HIDDEN - not shown for this size.</t>
-        </is>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est MASQUÉ - non affiché pour cette taille.</t>
-        </is>
-      </c>
-      <c r="J81" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K81" s="9"/>
-      <c r="L81" s="6"/>
-    </row>
-    <row r="82" spans="1:12">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any - sector-agnostic panel)</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is HIDDEN - not shown for this size.</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est MASQUÉ - non affiché pour cette taille.</t>
-        </is>
-      </c>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K82" s="9"/>
-      <c r="L82" s="6"/>
-    </row>
-    <row r="83" spans="1:12">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Large enterprise</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any - sector-agnostic panel)</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is SHOWN - this is the one size that reveals it.</t>
-        </is>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est AFFICHÉ - la seule taille qui le révèle.</t>
-        </is>
-      </c>
-      <c r="J83" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K83" s="9"/>
-      <c r="L83" s="6"/>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transformation or capital project</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Under $1 million in annual revenue</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AgriMarketing SME stream is SHOWN. AgriMarketing NIA stream is HIDDEN.</t>
-        </is>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le volet PME d'Agri-marketing est AFFICHÉ. Le volet ANI est MASQUÉ.</t>
-        </is>
-      </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K84" s="9"/>
-      <c r="L84" s="6"/>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transformation or capital project</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Non-profit, association, board of trade</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AgriMarketing SME stream is HIDDEN. AgriMarketing NIA stream is SHOWN - this is the one size that reveals it.</t>
-        </is>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le volet PME d'Agri-marketing est MASQUÉ. Le volet ANI est AFFICHÉ - la seule taille qui le révèle.</t>
-        </is>
-      </c>
-      <c r="J85" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K85" s="9"/>
-      <c r="L85" s="6"/>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transformation or capital project</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AgriMarketing SME stream is SHOWN. AgriMarketing NIA stream is HIDDEN.</t>
-        </is>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le volet PME d'Agri-marketing est AFFICHÉ. Le volet ANI est MASQUÉ.</t>
-        </is>
-      </c>
-      <c r="J86" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K86" s="9"/>
-      <c r="L86" s="6"/>
-    </row>
-    <row r="87" spans="1:12">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transformation or capital project</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AgriMarketing SME stream is SHOWN. AgriMarketing NIA stream is HIDDEN.</t>
-        </is>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le volet PME d'Agri-marketing est AFFICHÉ. Le volet ANI est MASQUÉ.</t>
-        </is>
-      </c>
-      <c r="J87" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K87" s="9"/>
-      <c r="L87" s="6"/>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transformation or capital project</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Large enterprise</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AgriMarketing SME stream is SHOWN. AgriMarketing NIA stream is HIDDEN.</t>
-        </is>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le volet PME d'Agri-marketing est AFFICHÉ. Le volet ANI est MASQUÉ.</t>
-        </is>
-      </c>
-      <c r="J88" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K88" s="9"/>
-      <c r="L88" s="6"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L88"/>
+  <autoFilter ref="A1:L65"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J88">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J65">
       <formula1>"Open,Needs change,Approved"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8806,7 +7377,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative (national hub, liquidity/transformation agnostic) + per-region variants in the regional programs block</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - per-region variants in the Decision Tree tab's regional programs block (the old national-hub line was dropped in the 2026-09-04 update; the regional links are now the only RTRI entry point, most gated to hide for "Under $1 million in annual revenue")</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
